--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122584217</v>
+        <v>122584460</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589660</v>
+        <v>589578</v>
       </c>
       <c r="R2" t="n">
-        <v>6573533</v>
+        <v>6573480</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +772,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1098,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584460</v>
+        <v>122584217</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1114,46 +1123,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589578</v>
+        <v>589660</v>
       </c>
       <c r="R5" t="n">
-        <v>6573480</v>
+        <v>6573533</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,12 +1200,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1234,6 +1234,1240 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122592249</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90762</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kräftaslätten, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>589898</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6573622</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122592583</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>589579</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6573463</v>
+      </c>
+      <c r="S7" t="n">
+        <v>13</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122592434</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fruns sved, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589654</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6573497</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122593020</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589574</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6573376</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122593786</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>589454</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6573404</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122592725</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43727</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>589591</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6573438</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122592362</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56593</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fruns sved, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>589659</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6573480</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122592155</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kräftaslätten, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>589876</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6573672</v>
+      </c>
+      <c r="S13" t="n">
+        <v>13</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122592929</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79274</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>589577</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6573401</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer på stubbe i hällmarksskogen</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122592276</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57753</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kräftaslätten, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>589900</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6573616</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592725</v>
+        <v>122592362</v>
       </c>
       <c r="B11" t="n">
-        <v>43727</v>
+        <v>56593</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1866,21 +1866,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1888,21 +1888,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589591</v>
+        <v>589659</v>
       </c>
       <c r="R11" t="n">
-        <v>6573438</v>
+        <v>6573480</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1934,7 +1945,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,7 +1955,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1971,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122592362</v>
+        <v>122592725</v>
       </c>
       <c r="B12" t="n">
-        <v>56593</v>
+        <v>43727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1987,21 +2003,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>101735</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2009,32 +2025,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589659</v>
+        <v>589591</v>
       </c>
       <c r="R12" t="n">
-        <v>6573480</v>
+        <v>6573438</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -2066,7 +2071,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2076,12 +2081,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -814,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122584161</v>
+        <v>122584217</v>
       </c>
       <c r="B3" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,30 +830,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -861,10 +862,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589846</v>
+        <v>589660</v>
       </c>
       <c r="R3" t="n">
-        <v>6573623</v>
+        <v>6573533</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,12 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på granlåga</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +916,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -931,22 +926,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122584482</v>
+        <v>122584161</v>
       </c>
       <c r="B4" t="n">
-        <v>57299</v>
+        <v>90839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -980,53 +960,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589530</v>
+        <v>589846</v>
       </c>
       <c r="R4" t="n">
-        <v>6573435</v>
+        <v>6573623</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1055,7 +1026,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1065,12 +1036,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1079,6 +1050,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1089,7 +1061,22 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1107,10 +1094,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584217</v>
+        <v>122584482</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,16 +1110,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1140,28 +1127,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589660</v>
+        <v>589530</v>
       </c>
       <c r="R5" t="n">
-        <v>6573533</v>
+        <v>6573435</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1190,7 +1185,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1200,7 +1195,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592249</v>
+        <v>122592276</v>
       </c>
       <c r="B6" t="n">
-        <v>90762</v>
+        <v>57753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,30 +1249,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1280,13 +1289,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589898</v>
+        <v>589900</v>
       </c>
       <c r="R6" t="n">
-        <v>6573622</v>
+        <v>6573616</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1315,7 +1324,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1325,12 +1334,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1357,10 +1361,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592583</v>
+        <v>122593786</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1369,38 +1373,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1410,13 +1408,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589579</v>
+        <v>589454</v>
       </c>
       <c r="R7" t="n">
-        <v>6573463</v>
+        <v>6573404</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1445,7 +1443,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1455,7 +1453,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1606,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122593020</v>
+        <v>122592929</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>79274</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1618,38 +1616,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1659,13 +1651,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589574</v>
+        <v>589577</v>
       </c>
       <c r="R9" t="n">
-        <v>6573376</v>
+        <v>6573401</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1694,7 +1686,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1704,7 +1696,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer på stubbe i hällmarksskogen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1731,10 +1728,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122593786</v>
+        <v>122593020</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1743,32 +1740,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1778,13 +1781,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589454</v>
+        <v>589574</v>
       </c>
       <c r="R10" t="n">
-        <v>6573404</v>
+        <v>6573376</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1816,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1826,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1853,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592362</v>
+        <v>122592583</v>
       </c>
       <c r="B11" t="n">
-        <v>56593</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1866,21 +1869,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1888,35 +1891,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589659</v>
+        <v>589579</v>
       </c>
       <c r="R11" t="n">
-        <v>6573480</v>
+        <v>6573463</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1945,7 +1941,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1955,12 +1951,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1987,10 +1978,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122592725</v>
+        <v>122592362</v>
       </c>
       <c r="B12" t="n">
-        <v>43727</v>
+        <v>56593</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,21 +1994,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101735</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2025,21 +2016,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589591</v>
+        <v>589659</v>
       </c>
       <c r="R12" t="n">
-        <v>6573438</v>
+        <v>6573480</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -2071,7 +2073,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2081,7 +2083,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2223,10 +2230,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592929</v>
+        <v>122592725</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>43727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2235,34 +2242,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2270,13 +2279,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589577</v>
+        <v>589591</v>
       </c>
       <c r="R14" t="n">
-        <v>6573401</v>
+        <v>6573438</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2305,7 +2314,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2315,12 +2324,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer på stubbe i hällmarksskogen</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2347,10 +2351,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122592276</v>
+        <v>122592249</v>
       </c>
       <c r="B15" t="n">
-        <v>57753</v>
+        <v>90762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2359,39 +2363,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>3242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2399,13 +2394,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589900</v>
+        <v>589898</v>
       </c>
       <c r="R15" t="n">
-        <v>6573616</v>
+        <v>6573622</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2434,7 +2429,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2444,7 +2439,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -2230,10 +2230,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592725</v>
+        <v>122592249</v>
       </c>
       <c r="B14" t="n">
-        <v>43727</v>
+        <v>90762</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2242,47 +2242,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589591</v>
+        <v>589898</v>
       </c>
       <c r="R14" t="n">
-        <v>6573438</v>
+        <v>6573622</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2314,7 +2308,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2324,7 +2318,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2351,10 +2350,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122592249</v>
+        <v>122592725</v>
       </c>
       <c r="B15" t="n">
-        <v>90762</v>
+        <v>43727</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2363,41 +2362,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589898</v>
+        <v>589591</v>
       </c>
       <c r="R15" t="n">
-        <v>6573622</v>
+        <v>6573438</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2429,7 +2434,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2439,12 +2444,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122584460</v>
+        <v>122584161</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589578</v>
+        <v>589846</v>
       </c>
       <c r="R2" t="n">
-        <v>6573480</v>
+        <v>6573623</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,12 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,7 +792,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +825,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122584217</v>
+        <v>122584482</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,16 +841,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -847,28 +858,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589660</v>
+        <v>589530</v>
       </c>
       <c r="R3" t="n">
-        <v>6573533</v>
+        <v>6573435</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +916,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +926,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -944,10 +968,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122584161</v>
+        <v>122584217</v>
       </c>
       <c r="B4" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,30 +984,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -991,10 +1016,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589846</v>
+        <v>589660</v>
       </c>
       <c r="R4" t="n">
-        <v>6573623</v>
+        <v>6573533</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,7 +1051,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1061,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer på granlåga</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1070,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1061,22 +1080,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1094,10 +1098,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584482</v>
+        <v>122584460</v>
       </c>
       <c r="B5" t="n">
-        <v>57299</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1110,37 +1114,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589530</v>
+        <v>589578</v>
       </c>
       <c r="R5" t="n">
-        <v>6573435</v>
+        <v>6573480</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592276</v>
+        <v>122593020</v>
       </c>
       <c r="B6" t="n">
-        <v>57753</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1275,27 +1275,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589900</v>
+        <v>589574</v>
       </c>
       <c r="R6" t="n">
-        <v>6573616</v>
+        <v>6573376</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1324,7 +1325,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1334,7 +1335,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1361,10 +1362,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122593786</v>
+        <v>122592276</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>57753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1373,48 +1374,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589454</v>
+        <v>589900</v>
       </c>
       <c r="R7" t="n">
-        <v>6573404</v>
+        <v>6573616</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1443,7 +1449,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1453,7 +1459,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1480,10 +1486,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122592434</v>
+        <v>122592362</v>
       </c>
       <c r="B8" t="n">
-        <v>79274</v>
+        <v>56593</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1492,32 +1498,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1527,13 +1546,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589654</v>
+        <v>589659</v>
       </c>
       <c r="R8" t="n">
-        <v>6573497</v>
+        <v>6573480</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1562,7 +1581,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1572,12 +1591,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer på silverved i äldre hällmarksskog.</t>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1728,10 +1747,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122593020</v>
+        <v>122592583</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1744,21 +1763,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1771,7 +1790,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1781,13 +1800,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589574</v>
+        <v>589579</v>
       </c>
       <c r="R10" t="n">
-        <v>6573376</v>
+        <v>6573463</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1816,7 +1835,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1826,7 +1845,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1853,10 +1872,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592583</v>
+        <v>122592155</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1865,51 +1884,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589579</v>
+        <v>589876</v>
       </c>
       <c r="R11" t="n">
-        <v>6573463</v>
+        <v>6573672</v>
       </c>
       <c r="S11" t="n">
         <v>13</v>
@@ -1941,7 +1950,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1951,7 +1960,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1978,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122592362</v>
+        <v>122593786</v>
       </c>
       <c r="B12" t="n">
-        <v>56593</v>
+        <v>79274</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1990,61 +1999,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589659</v>
+        <v>589454</v>
       </c>
       <c r="R12" t="n">
-        <v>6573480</v>
+        <v>6573404</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2073,7 +2069,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2083,12 +2079,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2115,10 +2106,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122592155</v>
+        <v>122592249</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>90755</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2131,21 +2122,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2158,13 +2149,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589876</v>
+        <v>589898</v>
       </c>
       <c r="R13" t="n">
-        <v>6573672</v>
+        <v>6573622</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2193,7 +2184,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2203,7 +2194,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2230,10 +2226,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592249</v>
+        <v>122592434</v>
       </c>
       <c r="B14" t="n">
-        <v>90762</v>
+        <v>79274</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2246,40 +2242,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589898</v>
+        <v>589654</v>
       </c>
       <c r="R14" t="n">
-        <v>6573622</v>
+        <v>6573497</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122584161</v>
+        <v>122584217</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589846</v>
+        <v>589660</v>
       </c>
       <c r="R2" t="n">
-        <v>6573623</v>
+        <v>6573533</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer på granlåga</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,22 +787,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -825,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122584482</v>
+        <v>122584161</v>
       </c>
       <c r="B3" t="n">
-        <v>57299</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,53 +821,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589530</v>
+        <v>589846</v>
       </c>
       <c r="R3" t="n">
-        <v>6573435</v>
+        <v>6573623</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -916,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -926,12 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,6 +911,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -950,7 +922,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -968,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122584217</v>
+        <v>122584460</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,42 +971,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589660</v>
+        <v>589578</v>
       </c>
       <c r="R4" t="n">
-        <v>6573533</v>
+        <v>6573480</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1051,7 +1042,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1061,7 +1052,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,10 +1094,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584460</v>
+        <v>122584482</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>57299</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1114,33 +1110,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589578</v>
+        <v>589530</v>
       </c>
       <c r="R5" t="n">
-        <v>6573480</v>
+        <v>6573435</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122593020</v>
+        <v>122592155</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>79274</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,54 +1249,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589574</v>
+        <v>589876</v>
       </c>
       <c r="R6" t="n">
-        <v>6573376</v>
+        <v>6573672</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1325,7 +1315,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1335,7 +1325,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1362,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592276</v>
+        <v>122592929</v>
       </c>
       <c r="B7" t="n">
-        <v>57753</v>
+        <v>79274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1374,53 +1364,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589900</v>
+        <v>589577</v>
       </c>
       <c r="R7" t="n">
-        <v>6573616</v>
+        <v>6573401</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1449,7 +1434,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1459,7 +1444,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på stubbe i hällmarksskogen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1486,10 +1476,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122592362</v>
+        <v>122592249</v>
       </c>
       <c r="B8" t="n">
-        <v>56593</v>
+        <v>90755</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1498,58 +1488,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589659</v>
+        <v>589898</v>
       </c>
       <c r="R8" t="n">
-        <v>6573480</v>
+        <v>6573622</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1581,7 +1554,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1591,12 +1564,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1623,10 +1596,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122592929</v>
+        <v>122592583</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1635,32 +1608,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1670,13 +1649,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589577</v>
+        <v>589579</v>
       </c>
       <c r="R9" t="n">
-        <v>6573401</v>
+        <v>6573463</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1705,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1715,12 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växer på stubbe i hällmarksskogen</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1747,10 +1721,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122592583</v>
+        <v>122593786</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>79274</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1759,38 +1733,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1800,13 +1768,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589579</v>
+        <v>589454</v>
       </c>
       <c r="R10" t="n">
-        <v>6573463</v>
+        <v>6573404</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1835,7 +1803,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1845,7 +1813,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1872,10 +1840,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592155</v>
+        <v>122592725</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>43727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1884,44 +1852,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589876</v>
+        <v>589591</v>
       </c>
       <c r="R11" t="n">
-        <v>6573672</v>
+        <v>6573438</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1950,7 +1924,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1960,7 +1934,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1987,10 +1961,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122593786</v>
+        <v>122593020</v>
       </c>
       <c r="B12" t="n">
-        <v>79274</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1999,32 +1973,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2034,13 +2014,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589454</v>
+        <v>589574</v>
       </c>
       <c r="R12" t="n">
-        <v>6573404</v>
+        <v>6573376</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2069,7 +2049,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,7 +2059,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2106,10 +2086,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122592249</v>
+        <v>122592434</v>
       </c>
       <c r="B13" t="n">
-        <v>90755</v>
+        <v>79274</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2122,40 +2102,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589898</v>
+        <v>589654</v>
       </c>
       <c r="R13" t="n">
-        <v>6573622</v>
+        <v>6573497</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2184,7 +2168,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2194,12 +2178,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2226,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592434</v>
+        <v>122592362</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>56593</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2238,32 +2222,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2273,13 +2270,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589654</v>
+        <v>589659</v>
       </c>
       <c r="R14" t="n">
-        <v>6573497</v>
+        <v>6573480</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2308,7 +2305,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2318,12 +2315,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer på silverved i äldre hällmarksskog.</t>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2350,10 +2347,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122592725</v>
+        <v>122592276</v>
       </c>
       <c r="B15" t="n">
-        <v>43727</v>
+        <v>57753</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2366,21 +2363,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101735</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2388,24 +2385,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589591</v>
+        <v>589900</v>
       </c>
       <c r="R15" t="n">
-        <v>6573438</v>
+        <v>6573616</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122584217</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122584161</v>
+        <v>122584482</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>57300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,44 +821,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589846</v>
+        <v>589530</v>
       </c>
       <c r="R3" t="n">
-        <v>6573623</v>
+        <v>6573435</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +906,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer på granlåga</t>
+          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +920,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -922,22 +930,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -955,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122584460</v>
+        <v>122584161</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>90834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,46 +964,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589578</v>
+        <v>589846</v>
       </c>
       <c r="R4" t="n">
-        <v>6573480</v>
+        <v>6573623</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1042,7 +1030,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1052,12 +1040,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1066,6 +1054,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1076,7 +1065,22 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1094,10 +1098,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584482</v>
+        <v>122584460</v>
       </c>
       <c r="B5" t="n">
-        <v>57299</v>
+        <v>57537</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1110,37 +1114,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589530</v>
+        <v>589578</v>
       </c>
       <c r="R5" t="n">
-        <v>6573435</v>
+        <v>6573480</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592155</v>
+        <v>122592725</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>43728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,44 +1249,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589876</v>
+        <v>589591</v>
       </c>
       <c r="R6" t="n">
-        <v>6573672</v>
+        <v>6573438</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1315,7 +1321,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1325,7 +1331,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,10 +1358,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592929</v>
+        <v>122592249</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>90756</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1368,44 +1374,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589577</v>
+        <v>589898</v>
       </c>
       <c r="R7" t="n">
-        <v>6573401</v>
+        <v>6573622</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1434,7 +1436,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1444,12 +1446,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer på stubbe i hällmarksskogen</t>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1476,10 +1478,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122592249</v>
+        <v>122592434</v>
       </c>
       <c r="B8" t="n">
-        <v>90755</v>
+        <v>79275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1492,40 +1494,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589898</v>
+        <v>589654</v>
       </c>
       <c r="R8" t="n">
-        <v>6573622</v>
+        <v>6573497</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1554,7 +1560,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,12 +1570,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1596,10 +1602,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122592583</v>
+        <v>122593020</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1612,21 +1618,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1639,7 +1645,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1649,13 +1655,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589579</v>
+        <v>589574</v>
       </c>
       <c r="R9" t="n">
-        <v>6573463</v>
+        <v>6573376</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1684,7 +1690,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1700,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,10 +1727,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122593786</v>
+        <v>122592583</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1733,32 +1739,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1768,13 +1780,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589454</v>
+        <v>589579</v>
       </c>
       <c r="R10" t="n">
-        <v>6573404</v>
+        <v>6573463</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1803,7 +1815,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1813,7 +1825,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1840,10 +1852,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592725</v>
+        <v>122592929</v>
       </c>
       <c r="B11" t="n">
-        <v>43727</v>
+        <v>79275</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1852,36 +1864,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1889,13 +1899,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589591</v>
+        <v>589577</v>
       </c>
       <c r="R11" t="n">
-        <v>6573438</v>
+        <v>6573401</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1924,7 +1934,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1934,7 +1944,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer på stubbe i hällmarksskogen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1961,10 +1976,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122593020</v>
+        <v>122592155</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>79275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1973,54 +1988,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589574</v>
+        <v>589876</v>
       </c>
       <c r="R12" t="n">
-        <v>6573376</v>
+        <v>6573672</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2049,7 +2054,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2059,7 +2064,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2086,10 +2091,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122592434</v>
+        <v>122592362</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>56594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2098,32 +2103,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2133,13 +2151,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589654</v>
+        <v>589659</v>
       </c>
       <c r="R13" t="n">
-        <v>6573497</v>
+        <v>6573480</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2168,7 +2186,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2178,12 +2196,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Växer på silverved i äldre hällmarksskog.</t>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2210,10 +2228,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592362</v>
+        <v>122593786</v>
       </c>
       <c r="B14" t="n">
-        <v>56593</v>
+        <v>79275</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2222,61 +2240,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589659</v>
+        <v>589454</v>
       </c>
       <c r="R14" t="n">
-        <v>6573480</v>
+        <v>6573404</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2305,7 +2310,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2315,12 +2320,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2350,7 +2350,7 @@
         <v>122592276</v>
       </c>
       <c r="B15" t="n">
-        <v>57753</v>
+        <v>57754</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,293 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122688962</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57300</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>589559</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6573426</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Senast jag besökte denna skog såg jag adult havsörn på samma plats. Rastande i höga gamla tallar på hällmarken.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122690527</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90857</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Elefantberget, Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>589565</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6573446</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Växer på knotig tall.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122584482</v>
+        <v>122584460</v>
       </c>
       <c r="B3" t="n">
-        <v>57300</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,37 +821,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -861,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589530</v>
+        <v>589578</v>
       </c>
       <c r="R3" t="n">
-        <v>6573435</v>
+        <v>6573480</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -911,7 +907,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -951,7 +947,7 @@
         <v>122584161</v>
       </c>
       <c r="B4" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1098,10 +1094,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584460</v>
+        <v>122584482</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
+        <v>57300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1114,33 +1110,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589578</v>
+        <v>589530</v>
       </c>
       <c r="R5" t="n">
-        <v>6573480</v>
+        <v>6573435</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592725</v>
+        <v>122592434</v>
       </c>
       <c r="B6" t="n">
-        <v>43728</v>
+        <v>79278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,50 +1249,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589591</v>
+        <v>589654</v>
       </c>
       <c r="R6" t="n">
-        <v>6573438</v>
+        <v>6573497</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1321,7 +1319,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1331,7 +1329,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1358,10 +1361,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592249</v>
+        <v>122592929</v>
       </c>
       <c r="B7" t="n">
-        <v>90756</v>
+        <v>79278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1374,40 +1377,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589898</v>
+        <v>589577</v>
       </c>
       <c r="R7" t="n">
-        <v>6573622</v>
+        <v>6573401</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1436,7 +1443,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1446,12 +1453,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>Växer på stubbe i hällmarksskogen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1478,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122592434</v>
+        <v>122592276</v>
       </c>
       <c r="B8" t="n">
-        <v>79275</v>
+        <v>57754</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1490,48 +1497,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589654</v>
+        <v>589900</v>
       </c>
       <c r="R8" t="n">
-        <v>6573497</v>
+        <v>6573616</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1560,7 +1572,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1570,12 +1582,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer på silverved i äldre hällmarksskog.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1602,10 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122593020</v>
+        <v>122592725</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>43728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1618,21 +1625,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1643,11 +1650,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1655,13 +1658,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589574</v>
+        <v>589591</v>
       </c>
       <c r="R9" t="n">
-        <v>6573376</v>
+        <v>6573438</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1690,7 +1693,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1700,7 +1703,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,10 +1730,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122592583</v>
+        <v>122592155</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1739,51 +1742,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589579</v>
+        <v>589876</v>
       </c>
       <c r="R10" t="n">
-        <v>6573463</v>
+        <v>6573672</v>
       </c>
       <c r="S10" t="n">
         <v>13</v>
@@ -1815,7 +1808,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1825,7 +1818,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,10 +1845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592929</v>
+        <v>122592583</v>
       </c>
       <c r="B11" t="n">
-        <v>79275</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1864,32 +1857,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1899,13 +1898,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589577</v>
+        <v>589579</v>
       </c>
       <c r="R11" t="n">
-        <v>6573401</v>
+        <v>6573463</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1934,7 +1933,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,12 +1943,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer på stubbe i hällmarksskogen</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1976,10 +1970,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122592155</v>
+        <v>122593786</v>
       </c>
       <c r="B12" t="n">
-        <v>79275</v>
+        <v>79278</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2011,21 +2005,25 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589876</v>
+        <v>589454</v>
       </c>
       <c r="R12" t="n">
-        <v>6573672</v>
+        <v>6573404</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2054,7 +2052,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2064,7 +2062,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2091,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122592362</v>
+        <v>122593020</v>
       </c>
       <c r="B13" t="n">
-        <v>56594</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2107,21 +2105,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2129,35 +2127,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589659</v>
+        <v>589574</v>
       </c>
       <c r="R13" t="n">
-        <v>6573480</v>
+        <v>6573376</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2186,7 +2177,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2196,12 +2187,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2228,10 +2214,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122593786</v>
+        <v>122592362</v>
       </c>
       <c r="B14" t="n">
-        <v>79275</v>
+        <v>56594</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2240,48 +2226,61 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589454</v>
+        <v>589659</v>
       </c>
       <c r="R14" t="n">
-        <v>6573404</v>
+        <v>6573480</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2310,7 +2309,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2320,7 +2319,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2347,10 +2351,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122592276</v>
+        <v>122592249</v>
       </c>
       <c r="B15" t="n">
-        <v>57754</v>
+        <v>90759</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2359,39 +2363,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>3242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2399,13 +2394,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589900</v>
+        <v>589898</v>
       </c>
       <c r="R15" t="n">
-        <v>6573616</v>
+        <v>6573622</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2434,7 +2429,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2444,7 +2439,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122584460</v>
+        <v>122584161</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>90837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,46 +821,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589578</v>
+        <v>589846</v>
       </c>
       <c r="R3" t="n">
-        <v>6573480</v>
+        <v>6573623</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +911,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -926,7 +922,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -944,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122584161</v>
+        <v>122584460</v>
       </c>
       <c r="B4" t="n">
-        <v>90837</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,41 +971,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589846</v>
+        <v>589578</v>
       </c>
       <c r="R4" t="n">
-        <v>6573623</v>
+        <v>6573480</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,7 +1042,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1036,12 +1052,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer på granlåga</t>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1066,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1061,22 +1076,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592434</v>
+        <v>122592583</v>
       </c>
       <c r="B6" t="n">
-        <v>79278</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,48 +1249,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589654</v>
+        <v>589579</v>
       </c>
       <c r="R6" t="n">
-        <v>6573497</v>
+        <v>6573463</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1319,7 +1325,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1329,12 +1335,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer på silverved i äldre hällmarksskog.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1361,7 +1362,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592929</v>
+        <v>122592155</v>
       </c>
       <c r="B7" t="n">
         <v>79278</v>
@@ -1396,25 +1397,21 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589577</v>
+        <v>589876</v>
       </c>
       <c r="R7" t="n">
-        <v>6573401</v>
+        <v>6573672</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1443,7 +1440,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1453,12 +1450,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer på stubbe i hällmarksskogen</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1730,10 +1722,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122592155</v>
+        <v>122592362</v>
       </c>
       <c r="B10" t="n">
-        <v>79278</v>
+        <v>56594</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1742,44 +1734,61 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589876</v>
+        <v>589659</v>
       </c>
       <c r="R10" t="n">
-        <v>6573672</v>
+        <v>6573480</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1808,7 +1817,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1818,7 +1827,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,10 +1859,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592583</v>
+        <v>122592434</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>79278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,54 +1871,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589579</v>
+        <v>589654</v>
       </c>
       <c r="R11" t="n">
-        <v>6573463</v>
+        <v>6573497</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1933,7 +1941,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1943,7 +1951,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1970,7 +1983,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122593786</v>
+        <v>122592929</v>
       </c>
       <c r="B12" t="n">
         <v>79278</v>
@@ -2017,13 +2030,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589454</v>
+        <v>589577</v>
       </c>
       <c r="R12" t="n">
-        <v>6573404</v>
+        <v>6573401</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2052,7 +2065,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2062,7 +2075,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer på stubbe i hällmarksskogen</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2089,10 +2107,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122593020</v>
+        <v>122593786</v>
       </c>
       <c r="B13" t="n">
-        <v>5173</v>
+        <v>79278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,38 +2119,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2142,13 +2154,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589574</v>
+        <v>589454</v>
       </c>
       <c r="R13" t="n">
-        <v>6573376</v>
+        <v>6573404</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2177,7 +2189,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2187,7 +2199,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,10 +2226,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592362</v>
+        <v>122593020</v>
       </c>
       <c r="B14" t="n">
-        <v>56594</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2230,21 +2242,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2252,35 +2264,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589659</v>
+        <v>589574</v>
       </c>
       <c r="R14" t="n">
-        <v>6573480</v>
+        <v>6573376</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2309,7 +2314,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2319,12 +2324,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2471,10 +2471,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122688962</v>
+        <v>122690527</v>
       </c>
       <c r="B16" t="n">
-        <v>57300</v>
+        <v>90857</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100067</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2509,31 +2509,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589559</v>
+        <v>589565</v>
       </c>
       <c r="R16" t="n">
-        <v>6573426</v>
+        <v>6573446</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2562,7 +2557,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2572,12 +2567,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Senast jag besökte denna skog såg jag adult havsörn på samma plats. Rastande i höga gamla tallar på hällmarken.</t>
+          <t>Växer på knotig tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2586,8 +2581,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2604,10 +2625,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122690527</v>
+        <v>122688962</v>
       </c>
       <c r="B17" t="n">
-        <v>90857</v>
+        <v>57300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2620,21 +2641,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100067</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2642,26 +2663,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589565</v>
+        <v>589559</v>
       </c>
       <c r="R17" t="n">
-        <v>6573446</v>
+        <v>6573426</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2690,7 +2716,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2700,12 +2726,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växer på knotig tall.</t>
+          <t>Senast jag besökte denna skog såg jag adult havsörn på samma plats. Rastande i höga gamla tallar på hällmarken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,34 +2740,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2755,6 +2755,240 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122708106</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79278</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Elefantberget, Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>589436</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6573367</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122708081</v>
+      </c>
+      <c r="B19" t="n">
+        <v>95015</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Elefantberget, Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>589483</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6573399</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122592725</v>
+        <v>122592276</v>
       </c>
       <c r="B8" t="n">
-        <v>43822</v>
+        <v>57848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1497,21 +1497,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1519,24 +1519,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589591</v>
+        <v>589900</v>
       </c>
       <c r="R8" t="n">
-        <v>6573438</v>
+        <v>6573616</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1565,7 +1568,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1575,7 +1578,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1602,10 +1605,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122592276</v>
+        <v>122592725</v>
       </c>
       <c r="B9" t="n">
-        <v>57848</v>
+        <v>43822</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1618,21 +1621,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1640,27 +1643,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589900</v>
+        <v>589591</v>
       </c>
       <c r="R9" t="n">
-        <v>6573616</v>
+        <v>6573438</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -2474,7 +2474,7 @@
         <v>122690527</v>
       </c>
       <c r="B16" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>122708106</v>
       </c>
       <c r="B20" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122781184</v>
+        <v>122781185</v>
       </c>
       <c r="B21" t="n">
-        <v>90905</v>
+        <v>90964</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,44 +3142,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589517</v>
+        <v>589591</v>
       </c>
       <c r="R21" t="n">
-        <v>6573441</v>
+        <v>6573415</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3208,7 +3212,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3218,7 +3222,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3245,10 +3249,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122781183</v>
+        <v>122790172</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>98355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3257,50 +3261,61 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589535</v>
+        <v>589821</v>
       </c>
       <c r="R22" t="n">
-        <v>6573430</v>
+        <v>6573637</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3322,54 +3337,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781187</v>
+        <v>122781183</v>
       </c>
       <c r="B23" t="n">
-        <v>91350</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3382,26 +3407,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3409,10 +3440,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589525</v>
+        <v>589535</v>
       </c>
       <c r="R23" t="n">
-        <v>6573444</v>
+        <v>6573430</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3444,7 +3475,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3454,7 +3485,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3481,10 +3512,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122790172</v>
+        <v>122781187</v>
       </c>
       <c r="B24" t="n">
-        <v>98347</v>
+        <v>91354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3493,61 +3524,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589821</v>
+        <v>589525</v>
       </c>
       <c r="R24" t="n">
-        <v>6573637</v>
+        <v>6573444</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3569,64 +3583,54 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122781185</v>
+        <v>122781184</v>
       </c>
       <c r="B25" t="n">
-        <v>90960</v>
+        <v>90909</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3635,48 +3639,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589591</v>
+        <v>589517</v>
       </c>
       <c r="R25" t="n">
-        <v>6573415</v>
+        <v>6573441</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3742,10 +3742,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122797987</v>
+        <v>122798013</v>
       </c>
       <c r="B26" t="n">
-        <v>90940</v>
+        <v>4776</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3754,49 +3754,51 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589638</v>
+        <v>589608</v>
       </c>
       <c r="R26" t="n">
-        <v>6573473</v>
+        <v>6573540</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3866,10 +3868,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797974</v>
+        <v>122797991</v>
       </c>
       <c r="B27" t="n">
-        <v>92256</v>
+        <v>5193</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3878,49 +3880,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589562</v>
+        <v>589638</v>
       </c>
       <c r="R27" t="n">
-        <v>6573423</v>
+        <v>6573473</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3990,10 +3986,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797991</v>
+        <v>122797974</v>
       </c>
       <c r="B28" t="n">
-        <v>5193</v>
+        <v>92260</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4002,43 +3998,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589638</v>
+        <v>589562</v>
       </c>
       <c r="R28" t="n">
-        <v>6573473</v>
+        <v>6573423</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4108,10 +4110,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122797978</v>
+        <v>122797987</v>
       </c>
       <c r="B29" t="n">
-        <v>90960</v>
+        <v>90944</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4124,26 +4126,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4155,14 +4157,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 13, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589573</v>
+        <v>589638</v>
       </c>
       <c r="R29" t="n">
-        <v>6573455</v>
+        <v>6573473</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4232,10 +4234,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122798013</v>
+        <v>122797980</v>
       </c>
       <c r="B30" t="n">
-        <v>4776</v>
+        <v>5465</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4248,21 +4250,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>101377</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4271,7 +4273,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4281,14 +4283,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589608</v>
+        <v>589633</v>
       </c>
       <c r="R30" t="n">
-        <v>6573540</v>
+        <v>6573458</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4358,10 +4360,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122797980</v>
+        <v>122797978</v>
       </c>
       <c r="B31" t="n">
-        <v>5465</v>
+        <v>90964</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4370,51 +4372,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101377</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 13, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589633</v>
+        <v>589573</v>
       </c>
       <c r="R31" t="n">
-        <v>6573458</v>
+        <v>6573455</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122584161</v>
+        <v>122584217</v>
       </c>
       <c r="B2" t="n">
-        <v>90940</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589846</v>
+        <v>589660</v>
       </c>
       <c r="R2" t="n">
-        <v>6573623</v>
+        <v>6573533</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer på granlåga</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,22 +787,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -968,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122584460</v>
+        <v>122584161</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>90944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,46 +964,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589578</v>
+        <v>589846</v>
       </c>
       <c r="R4" t="n">
-        <v>6573480</v>
+        <v>6573623</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1055,7 +1030,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1065,12 +1040,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1079,6 +1054,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1089,7 +1065,22 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1107,10 +1098,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584217</v>
+        <v>122584460</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,42 +1114,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589660</v>
+        <v>589578</v>
       </c>
       <c r="R5" t="n">
-        <v>6573533</v>
+        <v>6573480</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1190,7 +1185,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1200,7 +1195,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1240,7 +1240,7 @@
         <v>122592249</v>
       </c>
       <c r="B6" t="n">
-        <v>90862</v>
+        <v>90866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>122592434</v>
       </c>
       <c r="B7" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122592276</v>
+        <v>122593786</v>
       </c>
       <c r="B8" t="n">
-        <v>57848</v>
+        <v>79384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1493,53 +1493,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589900</v>
+        <v>589454</v>
       </c>
       <c r="R8" t="n">
-        <v>6573616</v>
+        <v>6573404</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1568,7 +1563,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1578,7 +1573,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1605,10 +1600,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122592725</v>
+        <v>122592155</v>
       </c>
       <c r="B9" t="n">
-        <v>43822</v>
+        <v>79384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1617,50 +1612,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589591</v>
+        <v>589876</v>
       </c>
       <c r="R9" t="n">
-        <v>6573438</v>
+        <v>6573672</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1689,7 +1678,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1699,7 +1688,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1726,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122592362</v>
+        <v>122592725</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>43822</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1742,21 +1731,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1764,32 +1753,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589659</v>
+        <v>589591</v>
       </c>
       <c r="R10" t="n">
-        <v>6573480</v>
+        <v>6573438</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1821,7 +1799,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1831,12 +1809,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1863,10 +1836,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592583</v>
+        <v>122593020</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1879,21 +1852,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1906,7 +1879,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1916,13 +1889,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589579</v>
+        <v>589574</v>
       </c>
       <c r="R11" t="n">
-        <v>6573463</v>
+        <v>6573376</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1951,7 +1924,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1961,7 +1934,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1988,10 +1961,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122592155</v>
+        <v>122592276</v>
       </c>
       <c r="B12" t="n">
-        <v>79380</v>
+        <v>57848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2000,30 +1973,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2031,13 +2013,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589876</v>
+        <v>589900</v>
       </c>
       <c r="R12" t="n">
-        <v>6573672</v>
+        <v>6573616</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2066,7 +2048,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2076,7 +2058,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2103,10 +2085,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122593786</v>
+        <v>122592583</v>
       </c>
       <c r="B13" t="n">
-        <v>79380</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2115,32 +2097,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2150,13 +2138,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589454</v>
+        <v>589579</v>
       </c>
       <c r="R13" t="n">
-        <v>6573404</v>
+        <v>6573463</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2185,7 +2173,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2195,7 +2183,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2222,10 +2210,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122593020</v>
+        <v>122592929</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>79384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2234,38 +2222,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2275,13 +2257,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589574</v>
+        <v>589577</v>
       </c>
       <c r="R14" t="n">
-        <v>6573376</v>
+        <v>6573401</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2310,7 +2292,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2320,7 +2302,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer på stubbe i hällmarksskogen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2347,10 +2334,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122592929</v>
+        <v>122592362</v>
       </c>
       <c r="B15" t="n">
-        <v>79380</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2359,48 +2346,61 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589577</v>
+        <v>589659</v>
       </c>
       <c r="R15" t="n">
-        <v>6573401</v>
+        <v>6573480</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer på stubbe i hällmarksskogen</t>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3868,10 +3868,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797991</v>
+        <v>122797974</v>
       </c>
       <c r="B27" t="n">
-        <v>5193</v>
+        <v>92260</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3880,43 +3880,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589638</v>
+        <v>589562</v>
       </c>
       <c r="R27" t="n">
-        <v>6573473</v>
+        <v>6573423</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3986,10 +3992,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797974</v>
+        <v>122797991</v>
       </c>
       <c r="B28" t="n">
-        <v>92260</v>
+        <v>5193</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3998,49 +4004,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589562</v>
+        <v>589638</v>
       </c>
       <c r="R28" t="n">
-        <v>6573423</v>
+        <v>6573473</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4482,6 +4482,153 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122881537</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Elefantberget, Elefantberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>589403</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6573397</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Två björkar, döende, varav det ena trädet lever i toppen</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Dead tree stem # Betula</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Hörnell</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Hörnell</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122584217</v>
+        <v>122584482</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,28 +708,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589660</v>
+        <v>589530</v>
       </c>
       <c r="R2" t="n">
-        <v>6573533</v>
+        <v>6573435</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +766,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +776,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122584482</v>
+        <v>122584217</v>
       </c>
       <c r="B3" t="n">
-        <v>57394</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,16 +834,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,36 +851,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589530</v>
+        <v>589660</v>
       </c>
       <c r="R3" t="n">
-        <v>6573435</v>
+        <v>6573533</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,12 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -948,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122584161</v>
+        <v>122584460</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,41 +964,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589846</v>
+        <v>589578</v>
       </c>
       <c r="R4" t="n">
-        <v>6573623</v>
+        <v>6573480</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1030,7 +1035,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1040,12 +1045,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer på granlåga</t>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1059,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1065,22 +1069,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1098,10 +1087,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584460</v>
+        <v>122584161</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>90944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1114,46 +1103,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589578</v>
+        <v>589846</v>
       </c>
       <c r="R5" t="n">
-        <v>6573480</v>
+        <v>6573623</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,6 +1193,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1219,7 +1204,22 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592249</v>
+        <v>122592155</v>
       </c>
       <c r="B6" t="n">
-        <v>90866</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589898</v>
+        <v>589876</v>
       </c>
       <c r="R6" t="n">
-        <v>6573622</v>
+        <v>6573672</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1325,12 +1325,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592434</v>
+        <v>122592583</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1369,48 +1364,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589654</v>
+        <v>589579</v>
       </c>
       <c r="R7" t="n">
-        <v>6573497</v>
+        <v>6573463</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1439,7 +1440,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1449,12 +1450,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer på silverved i äldre hällmarksskog.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1481,10 +1477,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122593786</v>
+        <v>122592362</v>
       </c>
       <c r="B8" t="n">
-        <v>79384</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1493,48 +1489,61 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589454</v>
+        <v>589659</v>
       </c>
       <c r="R8" t="n">
-        <v>6573404</v>
+        <v>6573480</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1563,7 +1572,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1573,7 +1582,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1600,10 +1614,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122592155</v>
+        <v>122593020</v>
       </c>
       <c r="B9" t="n">
-        <v>79384</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1612,44 +1626,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589876</v>
+        <v>589574</v>
       </c>
       <c r="R9" t="n">
-        <v>6573672</v>
+        <v>6573376</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1678,7 +1702,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1688,7 +1712,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1715,10 +1739,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122592725</v>
+        <v>122593786</v>
       </c>
       <c r="B10" t="n">
-        <v>43822</v>
+        <v>79384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1727,36 +1751,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1764,13 +1786,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589591</v>
+        <v>589454</v>
       </c>
       <c r="R10" t="n">
-        <v>6573438</v>
+        <v>6573404</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1799,7 +1821,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1809,7 +1831,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1836,10 +1858,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122593020</v>
+        <v>122592434</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>79384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1848,54 +1870,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589574</v>
+        <v>589654</v>
       </c>
       <c r="R11" t="n">
-        <v>6573376</v>
+        <v>6573497</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1924,7 +1940,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1934,7 +1950,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2085,10 +2106,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122592583</v>
+        <v>122592725</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>43822</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2101,21 +2122,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2126,11 +2147,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2138,13 +2155,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589579</v>
+        <v>589591</v>
       </c>
       <c r="R13" t="n">
-        <v>6573463</v>
+        <v>6573438</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2173,7 +2190,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2183,7 +2200,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2334,10 +2351,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122592362</v>
+        <v>122592249</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>90866</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2346,58 +2363,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>3242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589659</v>
+        <v>589898</v>
       </c>
       <c r="R15" t="n">
-        <v>6573480</v>
+        <v>6573622</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122781185</v>
+        <v>122790172</v>
       </c>
       <c r="B21" t="n">
-        <v>90964</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,48 +3142,61 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589591</v>
+        <v>589821</v>
       </c>
       <c r="R21" t="n">
-        <v>6573415</v>
+        <v>6573637</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3205,54 +3218,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122790172</v>
+        <v>122781184</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3261,61 +3284,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589821</v>
+        <v>589517</v>
       </c>
       <c r="R22" t="n">
-        <v>6573637</v>
+        <v>6573441</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3337,64 +3343,54 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781183</v>
+        <v>122781185</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>90964</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3403,25 +3399,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3431,8 +3427,6 @@
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3440,13 +3434,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589535</v>
+        <v>589591</v>
       </c>
       <c r="R23" t="n">
-        <v>6573430</v>
+        <v>6573415</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3475,7 +3469,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3485,7 +3479,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3627,10 +3621,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122781184</v>
+        <v>122781183</v>
       </c>
       <c r="B25" t="n">
-        <v>90909</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3643,40 +3637,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589517</v>
+        <v>589535</v>
       </c>
       <c r="R25" t="n">
-        <v>6573441</v>
+        <v>6573430</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3742,10 +3742,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122798013</v>
+        <v>122797987</v>
       </c>
       <c r="B26" t="n">
-        <v>4776</v>
+        <v>90944</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3754,51 +3754,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589608</v>
+        <v>589638</v>
       </c>
       <c r="R26" t="n">
-        <v>6573540</v>
+        <v>6573473</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3868,10 +3866,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797974</v>
+        <v>122797991</v>
       </c>
       <c r="B27" t="n">
-        <v>92260</v>
+        <v>5193</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3880,49 +3878,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589562</v>
+        <v>589638</v>
       </c>
       <c r="R27" t="n">
-        <v>6573423</v>
+        <v>6573473</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3992,10 +3984,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797991</v>
+        <v>122797974</v>
       </c>
       <c r="B28" t="n">
-        <v>5193</v>
+        <v>92260</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4004,43 +3996,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589638</v>
+        <v>589562</v>
       </c>
       <c r="R28" t="n">
-        <v>6573473</v>
+        <v>6573423</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4110,10 +4108,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122797987</v>
+        <v>122797980</v>
       </c>
       <c r="B29" t="n">
-        <v>90944</v>
+        <v>5465</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4122,49 +4120,51 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>101377</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589638</v>
+        <v>589633</v>
       </c>
       <c r="R29" t="n">
-        <v>6573473</v>
+        <v>6573458</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122797980</v>
+        <v>122798013</v>
       </c>
       <c r="B30" t="n">
-        <v>5465</v>
+        <v>4776</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101377</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4283,14 +4283,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589633</v>
+        <v>589608</v>
       </c>
       <c r="R30" t="n">
-        <v>6573458</v>
+        <v>6573540</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122584482</v>
+        <v>122584161</v>
       </c>
       <c r="B2" t="n">
-        <v>57394</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,53 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100067</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589530</v>
+        <v>589846</v>
       </c>
       <c r="R2" t="n">
-        <v>6573435</v>
+        <v>6573623</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,12 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,6 +781,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,7 +792,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -948,10 +955,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122584460</v>
+        <v>122584482</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57394</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,33 +971,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1000,13 +1011,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589578</v>
+        <v>589530</v>
       </c>
       <c r="R4" t="n">
-        <v>6573480</v>
+        <v>6573435</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1050,7 +1061,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1087,10 +1098,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584161</v>
+        <v>122584460</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,41 +1114,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589846</v>
+        <v>589578</v>
       </c>
       <c r="R5" t="n">
-        <v>6573623</v>
+        <v>6573480</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1169,7 +1185,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1195,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer på granlåga</t>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1193,7 +1209,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1204,22 +1219,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592155</v>
+        <v>122592583</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>8441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,41 +1249,51 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589876</v>
+        <v>589579</v>
       </c>
       <c r="R6" t="n">
-        <v>6573672</v>
+        <v>6573463</v>
       </c>
       <c r="S6" t="n">
         <v>13</v>
@@ -1315,7 +1325,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1325,7 +1335,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,10 +1362,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592583</v>
+        <v>122592929</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1364,38 +1374,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589579</v>
+        <v>589577</v>
       </c>
       <c r="R7" t="n">
-        <v>6573463</v>
+        <v>6573401</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1440,7 +1444,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1450,7 +1454,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på stubbe i hällmarksskogen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1477,10 +1486,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122592362</v>
+        <v>122593020</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1493,21 +1502,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1515,35 +1524,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589659</v>
+        <v>589574</v>
       </c>
       <c r="R8" t="n">
-        <v>6573480</v>
+        <v>6573376</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1572,7 +1574,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1582,12 +1584,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1614,10 +1611,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122593020</v>
+        <v>122592276</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>57848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1630,21 +1627,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1652,28 +1649,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589574</v>
+        <v>589900</v>
       </c>
       <c r="R9" t="n">
-        <v>6573376</v>
+        <v>6573616</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1702,7 +1698,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1712,7 +1708,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1739,10 +1735,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122593786</v>
+        <v>122592249</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>90866</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1755,44 +1751,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589454</v>
+        <v>589898</v>
       </c>
       <c r="R10" t="n">
-        <v>6573404</v>
+        <v>6573622</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1821,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1831,7 +1823,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1858,7 +1855,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592434</v>
+        <v>122592155</v>
       </c>
       <c r="B11" t="n">
         <v>79384</v>
@@ -1893,25 +1890,21 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589654</v>
+        <v>589876</v>
       </c>
       <c r="R11" t="n">
-        <v>6573497</v>
+        <v>6573672</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1940,7 +1933,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1950,12 +1943,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer på silverved i äldre hällmarksskog.</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1982,10 +1970,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122592276</v>
+        <v>122592434</v>
       </c>
       <c r="B12" t="n">
-        <v>57848</v>
+        <v>79384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1994,53 +1982,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589900</v>
+        <v>589654</v>
       </c>
       <c r="R12" t="n">
-        <v>6573616</v>
+        <v>6573497</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2069,7 +2052,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,7 +2062,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2106,10 +2094,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122592725</v>
+        <v>122593786</v>
       </c>
       <c r="B13" t="n">
-        <v>43822</v>
+        <v>79384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2118,36 +2106,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2155,13 +2141,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589591</v>
+        <v>589454</v>
       </c>
       <c r="R13" t="n">
-        <v>6573438</v>
+        <v>6573404</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2190,7 +2176,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2200,7 +2186,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2227,10 +2213,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592929</v>
+        <v>122592725</v>
       </c>
       <c r="B14" t="n">
-        <v>79384</v>
+        <v>43822</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2239,34 +2225,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2274,13 +2262,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589577</v>
+        <v>589591</v>
       </c>
       <c r="R14" t="n">
-        <v>6573401</v>
+        <v>6573438</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2309,7 +2297,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2319,12 +2307,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer på stubbe i hällmarksskogen</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2351,10 +2334,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122592249</v>
+        <v>122592362</v>
       </c>
       <c r="B15" t="n">
-        <v>90866</v>
+        <v>56688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2363,41 +2346,58 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3242</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589898</v>
+        <v>589659</v>
       </c>
       <c r="R15" t="n">
-        <v>6573622</v>
+        <v>6573480</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2439,12 +2439,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2758,10 +2758,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122718073</v>
+        <v>122718165</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2807,17 +2807,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eklövens, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589532</v>
+        <v>589471</v>
       </c>
       <c r="R18" t="n">
-        <v>6573529</v>
+        <v>6573525</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2856,7 +2856,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tallåga i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,10 +2888,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122718165</v>
+        <v>122718073</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2899,21 +2904,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2932,17 +2937,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Eklövens, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589471</v>
+        <v>589532</v>
       </c>
       <c r="R19" t="n">
-        <v>6573525</v>
+        <v>6573529</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2971,7 +2976,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2981,12 +2986,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallåga i äldre hällmarksskog.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122790172</v>
+        <v>122781184</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,61 +3142,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589821</v>
+        <v>589517</v>
       </c>
       <c r="R21" t="n">
-        <v>6573637</v>
+        <v>6573441</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3218,64 +3201,54 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122781184</v>
+        <v>122781183</v>
       </c>
       <c r="B22" t="n">
-        <v>90909</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3288,40 +3261,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589517</v>
+        <v>589535</v>
       </c>
       <c r="R22" t="n">
-        <v>6573441</v>
+        <v>6573430</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3350,7 +3329,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3360,7 +3339,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3387,10 +3366,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781185</v>
+        <v>122790172</v>
       </c>
       <c r="B23" t="n">
-        <v>90964</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3399,48 +3378,61 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589591</v>
+        <v>589821</v>
       </c>
       <c r="R23" t="n">
-        <v>6573415</v>
+        <v>6573637</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3462,47 +3454,57 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3621,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122781183</v>
+        <v>122781185</v>
       </c>
       <c r="B25" t="n">
-        <v>5173</v>
+        <v>90964</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3633,25 +3635,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3661,8 +3663,6 @@
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3670,13 +3670,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589535</v>
+        <v>589591</v>
       </c>
       <c r="R25" t="n">
-        <v>6573430</v>
+        <v>6573415</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3742,10 +3742,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122797987</v>
+        <v>122797978</v>
       </c>
       <c r="B26" t="n">
-        <v>90944</v>
+        <v>90964</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3758,26 +3758,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3789,14 +3789,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 13, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589638</v>
+        <v>589573</v>
       </c>
       <c r="R26" t="n">
-        <v>6573473</v>
+        <v>6573455</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3866,10 +3866,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797991</v>
+        <v>122797980</v>
       </c>
       <c r="B27" t="n">
-        <v>5193</v>
+        <v>5465</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3882,39 +3882,47 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>101377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589638</v>
+        <v>589633</v>
       </c>
       <c r="R27" t="n">
-        <v>6573473</v>
+        <v>6573458</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3984,10 +3992,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797974</v>
+        <v>122797991</v>
       </c>
       <c r="B28" t="n">
-        <v>92260</v>
+        <v>5193</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3996,49 +4004,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589562</v>
+        <v>589638</v>
       </c>
       <c r="R28" t="n">
-        <v>6573423</v>
+        <v>6573473</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4108,10 +4110,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122797980</v>
+        <v>122798013</v>
       </c>
       <c r="B29" t="n">
-        <v>5465</v>
+        <v>4776</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4124,21 +4126,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101377</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4147,7 +4149,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4157,14 +4159,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589633</v>
+        <v>589608</v>
       </c>
       <c r="R29" t="n">
-        <v>6573458</v>
+        <v>6573540</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4234,10 +4236,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122798013</v>
+        <v>122797974</v>
       </c>
       <c r="B30" t="n">
-        <v>4776</v>
+        <v>92260</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4246,51 +4248,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589608</v>
+        <v>589562</v>
       </c>
       <c r="R30" t="n">
-        <v>6573540</v>
+        <v>6573423</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4360,10 +4360,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122797978</v>
+        <v>122797987</v>
       </c>
       <c r="B31" t="n">
-        <v>90964</v>
+        <v>90944</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4376,26 +4376,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4407,14 +4407,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kälbrolund 13, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589573</v>
+        <v>589638</v>
       </c>
       <c r="R31" t="n">
-        <v>6573455</v>
+        <v>6573473</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4629,6 +4629,454 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122911162</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kräftaslätten, Kräftaslätten, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>589636</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6573464</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122911262</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kräftaslätten, Kräftaslätten, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>589637</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6573466</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122910831</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kräftaslätten, Kräftaslätten, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>589587</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6573386</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122910913</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8430</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kräftaslätten, Kräftaslätten, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>589562</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6573412</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ella Axelsson Elfving</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -3866,10 +3866,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797980</v>
+        <v>122797991</v>
       </c>
       <c r="B27" t="n">
-        <v>5465</v>
+        <v>5193</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3882,47 +3882,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101377</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589633</v>
+        <v>589638</v>
       </c>
       <c r="R27" t="n">
-        <v>6573458</v>
+        <v>6573473</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3992,10 +3984,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797991</v>
+        <v>122797980</v>
       </c>
       <c r="B28" t="n">
-        <v>5193</v>
+        <v>5465</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4008,39 +4000,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>101377</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589638</v>
+        <v>589633</v>
       </c>
       <c r="R28" t="n">
-        <v>6573473</v>
+        <v>6573458</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122584161</v>
+        <v>122584482</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
+        <v>57394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589846</v>
+        <v>589530</v>
       </c>
       <c r="R2" t="n">
-        <v>6573623</v>
+        <v>6573435</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +766,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +776,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Växer på granlåga</t>
+          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +790,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,22 +800,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -825,10 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122584217</v>
+        <v>122584161</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,31 +834,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -873,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589660</v>
+        <v>589846</v>
       </c>
       <c r="R3" t="n">
-        <v>6573533</v>
+        <v>6573623</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +910,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,6 +924,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -937,7 +935,22 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -955,10 +968,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122584482</v>
+        <v>122584460</v>
       </c>
       <c r="B4" t="n">
-        <v>57394</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,37 +984,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1011,13 +1020,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589530</v>
+        <v>589578</v>
       </c>
       <c r="R4" t="n">
-        <v>6573435</v>
+        <v>6573480</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1061,7 +1070,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
+          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584460</v>
+        <v>122584217</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1114,46 +1123,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589578</v>
+        <v>589660</v>
       </c>
       <c r="R5" t="n">
-        <v>6573480</v>
+        <v>6573533</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1185,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,12 +1200,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Två talltitor i avverkningsanmäld hällmarksskog. Hällmarken håller höga naturvärden med flertalet naturvårdsarter.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592583</v>
+        <v>122592362</v>
       </c>
       <c r="B6" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1275,28 +1275,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589579</v>
+        <v>589659</v>
       </c>
       <c r="R6" t="n">
-        <v>6573463</v>
+        <v>6573480</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1325,7 +1332,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1335,7 +1342,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1362,7 +1374,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592929</v>
+        <v>122592434</v>
       </c>
       <c r="B7" t="n">
         <v>79384</v>
@@ -1405,17 +1417,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589577</v>
+        <v>589654</v>
       </c>
       <c r="R7" t="n">
-        <v>6573401</v>
+        <v>6573497</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1444,7 +1456,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1454,12 +1466,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer på stubbe i hällmarksskogen</t>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1486,10 +1498,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122593020</v>
+        <v>122592155</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>79384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1498,54 +1510,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589574</v>
+        <v>589876</v>
       </c>
       <c r="R8" t="n">
-        <v>6573376</v>
+        <v>6573672</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1574,7 +1576,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1584,7 +1586,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1611,10 +1613,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122592276</v>
+        <v>122592583</v>
       </c>
       <c r="B9" t="n">
-        <v>57848</v>
+        <v>8441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1627,21 +1629,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1649,27 +1651,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589900</v>
+        <v>589579</v>
       </c>
       <c r="R9" t="n">
-        <v>6573616</v>
+        <v>6573463</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1698,7 +1701,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1708,7 +1711,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1735,10 +1738,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122592249</v>
+        <v>122592929</v>
       </c>
       <c r="B10" t="n">
-        <v>90866</v>
+        <v>79384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1751,40 +1754,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589898</v>
+        <v>589577</v>
       </c>
       <c r="R10" t="n">
-        <v>6573622</v>
+        <v>6573401</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1813,7 +1820,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,12 +1830,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>Växer på stubbe i hällmarksskogen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1855,10 +1862,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592155</v>
+        <v>122592276</v>
       </c>
       <c r="B11" t="n">
-        <v>79384</v>
+        <v>57848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1867,30 +1874,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1898,13 +1914,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589876</v>
+        <v>589900</v>
       </c>
       <c r="R11" t="n">
-        <v>6573672</v>
+        <v>6573616</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1933,7 +1949,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1943,7 +1959,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1970,7 +1986,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122592434</v>
+        <v>122593786</v>
       </c>
       <c r="B12" t="n">
         <v>79384</v>
@@ -2013,17 +2029,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589654</v>
+        <v>589454</v>
       </c>
       <c r="R12" t="n">
-        <v>6573497</v>
+        <v>6573404</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2052,7 +2068,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2062,12 +2078,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer på silverved i äldre hällmarksskog.</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,10 +2105,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122593786</v>
+        <v>122592725</v>
       </c>
       <c r="B13" t="n">
-        <v>79384</v>
+        <v>43822</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2106,34 +2117,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>101735</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2141,13 +2154,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589454</v>
+        <v>589591</v>
       </c>
       <c r="R13" t="n">
-        <v>6573404</v>
+        <v>6573438</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2176,7 +2189,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2186,7 +2199,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2213,10 +2226,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592725</v>
+        <v>122592249</v>
       </c>
       <c r="B14" t="n">
-        <v>43822</v>
+        <v>90866</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2225,47 +2238,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101735</v>
+        <v>3242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589591</v>
+        <v>589898</v>
       </c>
       <c r="R14" t="n">
-        <v>6573438</v>
+        <v>6573622</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2297,7 +2304,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2307,7 +2314,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2334,10 +2346,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122592362</v>
+        <v>122593020</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2350,21 +2362,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2372,35 +2384,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589659</v>
+        <v>589574</v>
       </c>
       <c r="R15" t="n">
-        <v>6573480</v>
+        <v>6573376</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2429,7 +2434,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2439,12 +2444,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2758,10 +2758,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122718165</v>
+        <v>122718073</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2807,17 +2807,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Eklövens, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589471</v>
+        <v>589532</v>
       </c>
       <c r="R18" t="n">
-        <v>6573525</v>
+        <v>6573529</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2856,12 +2856,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tallåga i äldre hällmarksskog.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2888,10 +2883,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122718073</v>
+        <v>122718165</v>
       </c>
       <c r="B19" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2904,21 +2899,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2937,17 +2932,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eklövens, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589532</v>
+        <v>589471</v>
       </c>
       <c r="R19" t="n">
-        <v>6573529</v>
+        <v>6573525</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2976,7 +2971,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2986,7 +2981,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tallåga i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122781184</v>
+        <v>122781183</v>
       </c>
       <c r="B21" t="n">
-        <v>90909</v>
+        <v>5173</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3146,40 +3146,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589517</v>
+        <v>589535</v>
       </c>
       <c r="R21" t="n">
-        <v>6573441</v>
+        <v>6573430</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3208,7 +3214,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3218,7 +3224,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3245,10 +3251,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122781183</v>
+        <v>122781184</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>90909</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3261,46 +3267,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589535</v>
+        <v>589517</v>
       </c>
       <c r="R22" t="n">
-        <v>6573430</v>
+        <v>6573441</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3366,10 +3366,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122790172</v>
+        <v>122781185</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>90964</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3378,61 +3378,48 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589821</v>
+        <v>589591</v>
       </c>
       <c r="R23" t="n">
-        <v>6573637</v>
+        <v>6573415</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3454,64 +3441,54 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122781187</v>
+        <v>122790172</v>
       </c>
       <c r="B24" t="n">
-        <v>91354</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3520,44 +3497,61 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589525</v>
+        <v>589821</v>
       </c>
       <c r="R24" t="n">
-        <v>6573444</v>
+        <v>6573637</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3579,54 +3573,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122781185</v>
+        <v>122781187</v>
       </c>
       <c r="B25" t="n">
-        <v>90964</v>
+        <v>91354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3635,32 +3639,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3670,13 +3670,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589591</v>
+        <v>589525</v>
       </c>
       <c r="R25" t="n">
-        <v>6573415</v>
+        <v>6573444</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3866,10 +3866,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797991</v>
+        <v>122797980</v>
       </c>
       <c r="B27" t="n">
-        <v>5193</v>
+        <v>5465</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3882,39 +3882,47 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>101377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589638</v>
+        <v>589633</v>
       </c>
       <c r="R27" t="n">
-        <v>6573473</v>
+        <v>6573458</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3984,10 +3992,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797980</v>
+        <v>122797987</v>
       </c>
       <c r="B28" t="n">
-        <v>5465</v>
+        <v>90944</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3996,51 +4004,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589633</v>
+        <v>589638</v>
       </c>
       <c r="R28" t="n">
-        <v>6573458</v>
+        <v>6573473</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4110,10 +4116,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122798013</v>
+        <v>122797974</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>92260</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4122,51 +4128,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589608</v>
+        <v>589562</v>
       </c>
       <c r="R29" t="n">
-        <v>6573540</v>
+        <v>6573423</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4236,10 +4240,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122797974</v>
+        <v>122798013</v>
       </c>
       <c r="B30" t="n">
-        <v>92260</v>
+        <v>4776</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4248,49 +4252,51 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589562</v>
+        <v>589608</v>
       </c>
       <c r="R30" t="n">
-        <v>6573423</v>
+        <v>6573540</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4360,10 +4366,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122797987</v>
+        <v>122797991</v>
       </c>
       <c r="B31" t="n">
-        <v>90944</v>
+        <v>5193</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4372,38 +4378,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122911262</v>
+        <v>122910831</v>
       </c>
       <c r="B34" t="n">
-        <v>90944</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589637</v>
+        <v>589587</v>
       </c>
       <c r="R34" t="n">
-        <v>6573466</v>
+        <v>6573386</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910831</v>
+        <v>122911262</v>
       </c>
       <c r="B35" t="n">
-        <v>8441</v>
+        <v>90944</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4867,25 +4867,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589587</v>
+        <v>589637</v>
       </c>
       <c r="R35" t="n">
-        <v>6573386</v>
+        <v>6573466</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -1986,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122593786</v>
+        <v>122592249</v>
       </c>
       <c r="B12" t="n">
-        <v>79384</v>
+        <v>90866</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2002,44 +2002,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589454</v>
+        <v>589898</v>
       </c>
       <c r="R12" t="n">
-        <v>6573404</v>
+        <v>6573622</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2068,7 +2064,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2078,7 +2074,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2105,10 +2106,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122592725</v>
+        <v>122593786</v>
       </c>
       <c r="B13" t="n">
-        <v>43822</v>
+        <v>79384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2117,36 +2118,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2154,13 +2153,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589591</v>
+        <v>589454</v>
       </c>
       <c r="R13" t="n">
-        <v>6573438</v>
+        <v>6573404</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2189,7 +2188,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2199,7 +2198,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2226,10 +2225,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592249</v>
+        <v>122592725</v>
       </c>
       <c r="B14" t="n">
-        <v>90866</v>
+        <v>43822</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2238,41 +2237,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3242</v>
+        <v>101735</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589898</v>
+        <v>589591</v>
       </c>
       <c r="R14" t="n">
-        <v>6573622</v>
+        <v>6573438</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2304,7 +2309,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2314,12 +2319,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122584482</v>
+        <v>122584217</v>
       </c>
       <c r="B2" t="n">
-        <v>57394</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,36 +708,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Elefantberget, Srm</t>
+          <t>Norr om Elefantberget, Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589530</v>
+        <v>589660</v>
       </c>
       <c r="R2" t="n">
-        <v>6573435</v>
+        <v>6573533</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -776,12 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -818,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122584161</v>
+        <v>122584482</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>57394</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,44 +821,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Elefantberget, Fruns sved, Srm</t>
+          <t>Norr om Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589846</v>
+        <v>589530</v>
       </c>
       <c r="R3" t="n">
-        <v>6573623</v>
+        <v>6573435</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,12 +906,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer på granlåga</t>
+          <t>Havsörn satte sig i en tall på hällmarken. Adult med vit stjärt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +920,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -935,22 +930,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog. Hällmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Hällmarksskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1107,10 +1087,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122584217</v>
+        <v>122584161</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,31 +1103,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1155,10 +1134,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589660</v>
+        <v>589846</v>
       </c>
       <c r="R5" t="n">
-        <v>6573533</v>
+        <v>6573623</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1190,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1200,7 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,6 +1193,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1219,7 +1204,22 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Hällmarksskog</t>
+          <t>Barrskog. Hällmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592362</v>
+        <v>122592725</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>43822</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>101735</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1275,32 +1275,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589659</v>
+        <v>589591</v>
       </c>
       <c r="R6" t="n">
-        <v>6573480</v>
+        <v>6573438</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1332,7 +1321,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1342,12 +1331,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1374,10 +1358,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592434</v>
+        <v>122592362</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1386,32 +1370,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1421,13 +1418,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589654</v>
+        <v>589659</v>
       </c>
       <c r="R7" t="n">
-        <v>6573497</v>
+        <v>6573480</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1456,7 +1453,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1466,12 +1463,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer på silverved i äldre hällmarksskog.</t>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1498,7 +1495,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122592155</v>
+        <v>122592929</v>
       </c>
       <c r="B8" t="n">
         <v>79384</v>
@@ -1533,21 +1530,25 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589876</v>
+        <v>589577</v>
       </c>
       <c r="R8" t="n">
-        <v>6573672</v>
+        <v>6573401</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1576,7 +1577,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1586,7 +1587,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer på stubbe i hällmarksskogen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1613,10 +1619,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122592583</v>
+        <v>122592434</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>79384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1625,54 +1631,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589579</v>
+        <v>589654</v>
       </c>
       <c r="R9" t="n">
-        <v>6573463</v>
+        <v>6573497</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1711,7 +1711,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer på silverved i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1738,10 +1743,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122592929</v>
+        <v>122592276</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>57848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1750,48 +1755,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589577</v>
+        <v>589900</v>
       </c>
       <c r="R10" t="n">
-        <v>6573401</v>
+        <v>6573616</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1820,7 +1830,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1830,12 +1840,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Växer på stubbe i hällmarksskogen</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1862,10 +1867,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592276</v>
+        <v>122592249</v>
       </c>
       <c r="B11" t="n">
-        <v>57848</v>
+        <v>90874</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1874,39 +1879,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1914,13 +1910,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589900</v>
+        <v>589898</v>
       </c>
       <c r="R11" t="n">
-        <v>6573616</v>
+        <v>6573622</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1949,7 +1945,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1959,7 +1955,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1986,10 +1987,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122592249</v>
+        <v>122593786</v>
       </c>
       <c r="B12" t="n">
-        <v>90866</v>
+        <v>79384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2002,40 +2003,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589898</v>
+        <v>589454</v>
       </c>
       <c r="R12" t="n">
-        <v>6573622</v>
+        <v>6573404</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2064,7 +2069,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2074,12 +2079,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2106,10 +2106,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122593786</v>
+        <v>122593020</v>
       </c>
       <c r="B13" t="n">
-        <v>79384</v>
+        <v>5173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2118,32 +2118,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2153,13 +2159,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589454</v>
+        <v>589574</v>
       </c>
       <c r="R13" t="n">
-        <v>6573404</v>
+        <v>6573376</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2188,7 +2194,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2198,7 +2204,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2225,10 +2231,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122592725</v>
+        <v>122592155</v>
       </c>
       <c r="B14" t="n">
-        <v>43822</v>
+        <v>79384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2237,50 +2243,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101735</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589591</v>
+        <v>589876</v>
       </c>
       <c r="R14" t="n">
-        <v>6573438</v>
+        <v>6573672</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2346,10 +2346,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122593020</v>
+        <v>122592583</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2362,21 +2362,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2389,7 +2389,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589574</v>
+        <v>589579</v>
       </c>
       <c r="R15" t="n">
-        <v>6573376</v>
+        <v>6573463</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2471,10 +2471,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122690527</v>
+        <v>122688962</v>
       </c>
       <c r="B16" t="n">
-        <v>90964</v>
+        <v>57394</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100067</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2509,26 +2509,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589565</v>
+        <v>589559</v>
       </c>
       <c r="R16" t="n">
-        <v>6573446</v>
+        <v>6573426</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2557,7 +2562,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2567,12 +2572,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer på knotig tall.</t>
+          <t>Senast jag besökte denna skog såg jag adult havsörn på samma plats. Rastande i höga gamla tallar på hällmarken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2581,34 +2586,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2625,10 +2604,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122688962</v>
+        <v>122690527</v>
       </c>
       <c r="B17" t="n">
-        <v>57394</v>
+        <v>90972</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2641,21 +2620,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100067</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2663,31 +2642,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589559</v>
+        <v>589565</v>
       </c>
       <c r="R17" t="n">
-        <v>6573426</v>
+        <v>6573446</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2716,7 +2690,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2726,12 +2700,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Senast jag besökte denna skog såg jag adult havsörn på samma plats. Rastande i höga gamla tallar på hällmarken.</t>
+          <t>Växer på knotig tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2740,8 +2714,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2758,10 +2758,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122718073</v>
+        <v>122718165</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2807,17 +2807,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eklövens, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589532</v>
+        <v>589471</v>
       </c>
       <c r="R18" t="n">
-        <v>6573529</v>
+        <v>6573525</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2856,7 +2856,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tallåga i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,10 +2888,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122718165</v>
+        <v>122718073</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2899,21 +2904,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2932,17 +2937,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Eklövens, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589471</v>
+        <v>589532</v>
       </c>
       <c r="R19" t="n">
-        <v>6573525</v>
+        <v>6573529</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2971,7 +2976,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2981,12 +2986,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallåga i äldre hällmarksskog.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122781183</v>
+        <v>122781185</v>
       </c>
       <c r="B21" t="n">
-        <v>5173</v>
+        <v>90972</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,25 +3142,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3170,8 +3170,6 @@
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3179,13 +3177,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589535</v>
+        <v>589591</v>
       </c>
       <c r="R21" t="n">
-        <v>6573430</v>
+        <v>6573415</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3214,7 +3212,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3224,7 +3222,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3254,7 +3252,7 @@
         <v>122781184</v>
       </c>
       <c r="B22" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3366,10 +3364,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781185</v>
+        <v>122781183</v>
       </c>
       <c r="B23" t="n">
-        <v>90964</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3378,25 +3376,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3406,6 +3404,8 @@
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3413,13 +3413,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589591</v>
+        <v>589535</v>
       </c>
       <c r="R23" t="n">
-        <v>6573415</v>
+        <v>6573430</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3485,10 +3485,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122790172</v>
+        <v>122781187</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>91362</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3497,61 +3497,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589821</v>
+        <v>589525</v>
       </c>
       <c r="R24" t="n">
-        <v>6573637</v>
+        <v>6573444</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3573,64 +3556,54 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122781187</v>
+        <v>122790172</v>
       </c>
       <c r="B25" t="n">
-        <v>91354</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3639,44 +3612,61 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589525</v>
+        <v>589821</v>
       </c>
       <c r="R25" t="n">
-        <v>6573444</v>
+        <v>6573637</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3698,54 +3688,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122797978</v>
+        <v>122797974</v>
       </c>
       <c r="B26" t="n">
-        <v>90964</v>
+        <v>92268</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3758,21 +3758,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3789,14 +3789,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kälbrolund 13, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589573</v>
+        <v>589562</v>
       </c>
       <c r="R26" t="n">
-        <v>6573455</v>
+        <v>6573423</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3866,10 +3866,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797980</v>
+        <v>122797991</v>
       </c>
       <c r="B27" t="n">
-        <v>5465</v>
+        <v>5193</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3882,47 +3882,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101377</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589633</v>
+        <v>589638</v>
       </c>
       <c r="R27" t="n">
-        <v>6573458</v>
+        <v>6573473</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3992,10 +3984,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797987</v>
+        <v>122797978</v>
       </c>
       <c r="B28" t="n">
-        <v>90944</v>
+        <v>90972</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4008,26 +4000,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4039,14 +4031,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 13, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589638</v>
+        <v>589573</v>
       </c>
       <c r="R28" t="n">
-        <v>6573473</v>
+        <v>6573455</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4116,10 +4108,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122797974</v>
+        <v>122798013</v>
       </c>
       <c r="B29" t="n">
-        <v>92260</v>
+        <v>4776</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4128,49 +4120,51 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589562</v>
+        <v>589608</v>
       </c>
       <c r="R29" t="n">
-        <v>6573423</v>
+        <v>6573540</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4240,10 +4234,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122798013</v>
+        <v>122797987</v>
       </c>
       <c r="B30" t="n">
-        <v>4776</v>
+        <v>90952</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4252,51 +4246,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589608</v>
+        <v>589638</v>
       </c>
       <c r="R30" t="n">
-        <v>6573540</v>
+        <v>6573473</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4366,10 +4358,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122797991</v>
+        <v>122797980</v>
       </c>
       <c r="B31" t="n">
-        <v>5193</v>
+        <v>5465</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4382,39 +4374,47 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>101377</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589638</v>
+        <v>589633</v>
       </c>
       <c r="R31" t="n">
-        <v>6573473</v>
+        <v>6573458</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122911262</v>
+        <v>122910913</v>
       </c>
       <c r="B35" t="n">
-        <v>90944</v>
+        <v>8430</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4867,25 +4867,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589637</v>
+        <v>589562</v>
       </c>
       <c r="R35" t="n">
-        <v>6573466</v>
+        <v>6573412</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4967,10 +4967,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122910913</v>
+        <v>122911262</v>
       </c>
       <c r="B36" t="n">
-        <v>8430</v>
+        <v>90952</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4979,25 +4979,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589562</v>
+        <v>589637</v>
       </c>
       <c r="R36" t="n">
-        <v>6573412</v>
+        <v>6573466</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -1237,10 +1237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122592725</v>
+        <v>122592362</v>
       </c>
       <c r="B6" t="n">
-        <v>43822</v>
+        <v>56688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101735</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1275,21 +1275,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Fruns sved, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589591</v>
+        <v>589659</v>
       </c>
       <c r="R6" t="n">
-        <v>6573438</v>
+        <v>6573480</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1321,7 +1332,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1331,7 +1342,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stor tjädertupp flög upp från hällmarken.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1358,10 +1374,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122592362</v>
+        <v>122592725</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>43822</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1374,21 +1390,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>101735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1396,32 +1412,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fruns sved, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589659</v>
+        <v>589591</v>
       </c>
       <c r="R7" t="n">
-        <v>6573480</v>
+        <v>6573438</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1453,7 +1458,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1463,12 +1468,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stor tjädertupp flög upp från hällmarken.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1867,10 +1867,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122592249</v>
+        <v>122593786</v>
       </c>
       <c r="B11" t="n">
-        <v>90874</v>
+        <v>79384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1883,40 +1883,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kräftaslätten, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589898</v>
+        <v>589454</v>
       </c>
       <c r="R11" t="n">
-        <v>6573622</v>
+        <v>6573404</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1945,7 +1949,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1955,12 +1959,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer på gammal tallåga.</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1987,10 +1986,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122593786</v>
+        <v>122592249</v>
       </c>
       <c r="B12" t="n">
-        <v>79384</v>
+        <v>90874</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,44 +2002,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kräftaslätten, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589454</v>
+        <v>589898</v>
       </c>
       <c r="R12" t="n">
-        <v>6573404</v>
+        <v>6573622</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2069,7 +2064,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,7 +2074,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -2471,10 +2471,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122688962</v>
+        <v>122690527</v>
       </c>
       <c r="B16" t="n">
-        <v>57394</v>
+        <v>90972</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100067</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2509,31 +2509,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589559</v>
+        <v>589565</v>
       </c>
       <c r="R16" t="n">
-        <v>6573426</v>
+        <v>6573446</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2562,7 +2557,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2572,12 +2567,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Senast jag besökte denna skog såg jag adult havsörn på samma plats. Rastande i höga gamla tallar på hällmarken.</t>
+          <t>Växer på knotig tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2586,8 +2581,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2604,10 +2625,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122690527</v>
+        <v>122688962</v>
       </c>
       <c r="B17" t="n">
-        <v>90972</v>
+        <v>57394</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2620,21 +2641,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100067</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2642,26 +2663,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589565</v>
+        <v>589559</v>
       </c>
       <c r="R17" t="n">
-        <v>6573446</v>
+        <v>6573426</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2690,7 +2716,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2700,12 +2726,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Växer på knotig tall.</t>
+          <t>Senast jag besökte denna skog såg jag adult havsörn på samma plats. Rastande i höga gamla tallar på hällmarken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2714,34 +2740,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2758,10 +2758,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122718165</v>
+        <v>122718073</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2807,17 +2807,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Eklövens, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589471</v>
+        <v>589532</v>
       </c>
       <c r="R18" t="n">
-        <v>6573525</v>
+        <v>6573529</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2856,12 +2856,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På tallåga i äldre hällmarksskog.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2888,10 +2883,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122718073</v>
+        <v>122718165</v>
       </c>
       <c r="B19" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2904,21 +2899,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2937,17 +2932,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eklövens, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589532</v>
+        <v>589471</v>
       </c>
       <c r="R19" t="n">
-        <v>6573529</v>
+        <v>6573525</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2976,7 +2971,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2986,7 +2981,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tallåga i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122781185</v>
+        <v>122790172</v>
       </c>
       <c r="B21" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,48 +3142,61 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589591</v>
+        <v>589821</v>
       </c>
       <c r="R21" t="n">
-        <v>6573415</v>
+        <v>6573637</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3205,54 +3218,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122781184</v>
+        <v>122781187</v>
       </c>
       <c r="B22" t="n">
-        <v>90917</v>
+        <v>91362</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3265,21 +3288,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>5420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3288,17 +3311,17 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589517</v>
+        <v>589525</v>
       </c>
       <c r="R22" t="n">
-        <v>6573441</v>
+        <v>6573444</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3327,7 +3350,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3337,7 +3360,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3364,10 +3387,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781183</v>
+        <v>122781184</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>90917</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3380,46 +3403,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589535</v>
+        <v>589517</v>
       </c>
       <c r="R23" t="n">
-        <v>6573430</v>
+        <v>6573441</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3448,7 +3465,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3458,7 +3475,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3485,10 +3502,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122781187</v>
+        <v>122781183</v>
       </c>
       <c r="B24" t="n">
-        <v>91362</v>
+        <v>5173</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3501,26 +3518,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3528,10 +3551,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589525</v>
+        <v>589535</v>
       </c>
       <c r="R24" t="n">
-        <v>6573444</v>
+        <v>6573430</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3563,7 +3586,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3573,7 +3596,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3600,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122790172</v>
+        <v>122781185</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>90972</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3612,61 +3635,48 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589821</v>
+        <v>589591</v>
       </c>
       <c r="R25" t="n">
-        <v>6573637</v>
+        <v>6573415</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3688,64 +3698,54 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122797974</v>
+        <v>122797991</v>
       </c>
       <c r="B26" t="n">
-        <v>92268</v>
+        <v>5193</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3754,49 +3754,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589562</v>
+        <v>589638</v>
       </c>
       <c r="R26" t="n">
-        <v>6573423</v>
+        <v>6573473</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3866,10 +3860,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797991</v>
+        <v>122797987</v>
       </c>
       <c r="B27" t="n">
-        <v>5193</v>
+        <v>90952</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3878,32 +3872,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797978</v>
+        <v>122797980</v>
       </c>
       <c r="B28" t="n">
-        <v>90972</v>
+        <v>5465</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3996,49 +3996,51 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>101377</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 13, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589573</v>
+        <v>589633</v>
       </c>
       <c r="R28" t="n">
-        <v>6573455</v>
+        <v>6573458</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4108,10 +4110,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122798013</v>
+        <v>122797974</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>92268</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4120,51 +4122,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589608</v>
+        <v>589562</v>
       </c>
       <c r="R29" t="n">
-        <v>6573540</v>
+        <v>6573423</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122797987</v>
+        <v>122797978</v>
       </c>
       <c r="B30" t="n">
-        <v>90952</v>
+        <v>90972</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4250,26 +4250,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4281,14 +4281,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 13, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589638</v>
+        <v>589573</v>
       </c>
       <c r="R30" t="n">
-        <v>6573473</v>
+        <v>6573455</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122797980</v>
+        <v>122798013</v>
       </c>
       <c r="B31" t="n">
-        <v>5465</v>
+        <v>4776</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4374,21 +4374,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101377</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4397,7 +4397,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4407,14 +4407,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589633</v>
+        <v>589608</v>
       </c>
       <c r="R31" t="n">
-        <v>6573458</v>
+        <v>6573540</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910913</v>
+        <v>122911262</v>
       </c>
       <c r="B35" t="n">
-        <v>8430</v>
+        <v>90952</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4867,25 +4867,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589562</v>
+        <v>589637</v>
       </c>
       <c r="R35" t="n">
-        <v>6573412</v>
+        <v>6573466</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4967,10 +4967,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122911262</v>
+        <v>122910913</v>
       </c>
       <c r="B36" t="n">
-        <v>90952</v>
+        <v>8430</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4979,25 +4979,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589637</v>
+        <v>589562</v>
       </c>
       <c r="R36" t="n">
-        <v>6573466</v>
+        <v>6573412</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122790172</v>
+        <v>122781184</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,61 +3142,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589821</v>
+        <v>589517</v>
       </c>
       <c r="R21" t="n">
-        <v>6573637</v>
+        <v>6573441</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3218,64 +3201,54 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122781187</v>
+        <v>122781183</v>
       </c>
       <c r="B22" t="n">
-        <v>91362</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3288,26 +3261,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3315,10 +3294,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589525</v>
+        <v>589535</v>
       </c>
       <c r="R22" t="n">
-        <v>6573444</v>
+        <v>6573430</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3350,7 +3329,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3360,7 +3339,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3387,10 +3366,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781184</v>
+        <v>122781185</v>
       </c>
       <c r="B23" t="n">
-        <v>90917</v>
+        <v>90972</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3399,44 +3378,48 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589517</v>
+        <v>589591</v>
       </c>
       <c r="R23" t="n">
-        <v>6573441</v>
+        <v>6573415</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3465,7 +3448,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3475,7 +3458,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3502,10 +3485,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122781183</v>
+        <v>122790172</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3514,50 +3497,61 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589535</v>
+        <v>589821</v>
       </c>
       <c r="R24" t="n">
-        <v>6573430</v>
+        <v>6573637</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3579,54 +3573,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122781185</v>
+        <v>122781187</v>
       </c>
       <c r="B25" t="n">
-        <v>90972</v>
+        <v>91362</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3635,32 +3639,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3670,13 +3670,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589591</v>
+        <v>589525</v>
       </c>
       <c r="R25" t="n">
-        <v>6573415</v>
+        <v>6573444</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3742,10 +3742,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122797991</v>
+        <v>122797987</v>
       </c>
       <c r="B26" t="n">
-        <v>5193</v>
+        <v>90952</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3754,32 +3754,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3860,10 +3866,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797987</v>
+        <v>122798013</v>
       </c>
       <c r="B27" t="n">
-        <v>90952</v>
+        <v>4776</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3872,49 +3878,51 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589638</v>
+        <v>589608</v>
       </c>
       <c r="R27" t="n">
-        <v>6573473</v>
+        <v>6573540</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3984,10 +3992,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797980</v>
+        <v>122797991</v>
       </c>
       <c r="B28" t="n">
-        <v>5465</v>
+        <v>5193</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4000,47 +4008,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101377</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589633</v>
+        <v>589638</v>
       </c>
       <c r="R28" t="n">
-        <v>6573458</v>
+        <v>6573473</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122797974</v>
+        <v>122797978</v>
       </c>
       <c r="B29" t="n">
-        <v>92268</v>
+        <v>90972</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4126,21 +4126,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4157,14 +4157,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 13, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589562</v>
+        <v>589573</v>
       </c>
       <c r="R29" t="n">
-        <v>6573423</v>
+        <v>6573455</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4234,10 +4234,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122797978</v>
+        <v>122797980</v>
       </c>
       <c r="B30" t="n">
-        <v>90972</v>
+        <v>5465</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4246,49 +4246,51 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>101377</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 13, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589573</v>
+        <v>589633</v>
       </c>
       <c r="R30" t="n">
-        <v>6573455</v>
+        <v>6573458</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4358,10 +4360,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122798013</v>
+        <v>122797974</v>
       </c>
       <c r="B31" t="n">
-        <v>4776</v>
+        <v>92268</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4370,51 +4372,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589608</v>
+        <v>589562</v>
       </c>
       <c r="R31" t="n">
-        <v>6573540</v>
+        <v>6573423</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122910831</v>
+        <v>122911262</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>90952</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589587</v>
+        <v>589637</v>
       </c>
       <c r="R34" t="n">
-        <v>6573386</v>
+        <v>6573466</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122911262</v>
+        <v>122910913</v>
       </c>
       <c r="B35" t="n">
-        <v>90952</v>
+        <v>8430</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4867,25 +4867,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589637</v>
+        <v>589562</v>
       </c>
       <c r="R35" t="n">
-        <v>6573466</v>
+        <v>6573412</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4967,10 +4967,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122910913</v>
+        <v>122910831</v>
       </c>
       <c r="B36" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589562</v>
+        <v>589587</v>
       </c>
       <c r="R36" t="n">
-        <v>6573412</v>
+        <v>6573386</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -2471,10 +2471,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122690527</v>
+        <v>122688962</v>
       </c>
       <c r="B16" t="n">
-        <v>90972</v>
+        <v>57394</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>100067</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2509,26 +2509,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589565</v>
+        <v>589559</v>
       </c>
       <c r="R16" t="n">
-        <v>6573446</v>
+        <v>6573426</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2557,7 +2562,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2567,12 +2572,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer på knotig tall.</t>
+          <t>Senast jag besökte denna skog såg jag adult havsörn på samma plats. Rastande i höga gamla tallar på hällmarken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2581,34 +2586,8 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2625,10 +2604,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122688962</v>
+        <v>122690527</v>
       </c>
       <c r="B17" t="n">
-        <v>57394</v>
+        <v>90972</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2641,21 +2620,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100067</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2663,31 +2642,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589559</v>
+        <v>589565</v>
       </c>
       <c r="R17" t="n">
-        <v>6573426</v>
+        <v>6573446</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2716,7 +2690,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2726,12 +2700,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Senast jag besökte denna skog såg jag adult havsörn på samma plats. Rastande i höga gamla tallar på hällmarken.</t>
+          <t>Växer på knotig tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2740,8 +2714,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Hällmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2758,10 +2758,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122718073</v>
+        <v>122718165</v>
       </c>
       <c r="B18" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2807,17 +2807,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eklövens, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589532</v>
+        <v>589471</v>
       </c>
       <c r="R18" t="n">
-        <v>6573529</v>
+        <v>6573525</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2856,7 +2856,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tallåga i äldre hällmarksskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,10 +2888,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122718165</v>
+        <v>122718073</v>
       </c>
       <c r="B19" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2899,21 +2904,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2932,17 +2937,17 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Eklövens, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589471</v>
+        <v>589532</v>
       </c>
       <c r="R19" t="n">
-        <v>6573525</v>
+        <v>6573529</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2971,7 +2976,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2981,12 +2986,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tallåga i äldre hällmarksskog.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3245,10 +3245,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122781183</v>
+        <v>122790172</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3257,50 +3257,61 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589535</v>
+        <v>589821</v>
       </c>
       <c r="R22" t="n">
-        <v>6573430</v>
+        <v>6573637</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3322,54 +3333,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781185</v>
+        <v>122781183</v>
       </c>
       <c r="B23" t="n">
-        <v>90972</v>
+        <v>5173</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3378,25 +3399,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3406,6 +3427,8 @@
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3413,13 +3436,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589591</v>
+        <v>589535</v>
       </c>
       <c r="R23" t="n">
-        <v>6573415</v>
+        <v>6573430</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3448,7 +3471,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3458,7 +3481,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3485,10 +3508,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122790172</v>
+        <v>122781185</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>90972</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3497,61 +3520,48 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589821</v>
+        <v>589591</v>
       </c>
       <c r="R24" t="n">
-        <v>6573637</v>
+        <v>6573415</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3573,57 +3583,47 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3742,10 +3742,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122797987</v>
+        <v>122797991</v>
       </c>
       <c r="B26" t="n">
-        <v>90952</v>
+        <v>5193</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3754,38 +3754,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3866,10 +3860,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122798013</v>
+        <v>122797980</v>
       </c>
       <c r="B27" t="n">
-        <v>4776</v>
+        <v>5465</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3882,21 +3876,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>101377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3905,7 +3899,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3915,14 +3909,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589608</v>
+        <v>589633</v>
       </c>
       <c r="R27" t="n">
-        <v>6573540</v>
+        <v>6573458</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3992,10 +3986,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797991</v>
+        <v>122797974</v>
       </c>
       <c r="B28" t="n">
-        <v>5193</v>
+        <v>92268</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4004,43 +3998,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589638</v>
+        <v>589562</v>
       </c>
       <c r="R28" t="n">
-        <v>6573473</v>
+        <v>6573423</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122797978</v>
+        <v>122798013</v>
       </c>
       <c r="B29" t="n">
-        <v>90972</v>
+        <v>4776</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4122,49 +4122,51 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 13, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589573</v>
+        <v>589608</v>
       </c>
       <c r="R29" t="n">
-        <v>6573455</v>
+        <v>6573540</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4234,10 +4236,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122797980</v>
+        <v>122797987</v>
       </c>
       <c r="B30" t="n">
-        <v>5465</v>
+        <v>90952</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4246,51 +4248,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101377</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589633</v>
+        <v>589638</v>
       </c>
       <c r="R30" t="n">
-        <v>6573458</v>
+        <v>6573473</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4360,10 +4360,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122797974</v>
+        <v>122797978</v>
       </c>
       <c r="B31" t="n">
-        <v>92268</v>
+        <v>90972</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4376,21 +4376,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4407,14 +4407,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 13, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589562</v>
+        <v>589573</v>
       </c>
       <c r="R31" t="n">
-        <v>6573423</v>
+        <v>6573455</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122911262</v>
+        <v>122910913</v>
       </c>
       <c r="B34" t="n">
-        <v>90952</v>
+        <v>8430</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589637</v>
+        <v>589562</v>
       </c>
       <c r="R34" t="n">
-        <v>6573466</v>
+        <v>6573412</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910913</v>
+        <v>122910831</v>
       </c>
       <c r="B35" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589562</v>
+        <v>589587</v>
       </c>
       <c r="R35" t="n">
-        <v>6573412</v>
+        <v>6573386</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4967,10 +4967,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122910831</v>
+        <v>122911262</v>
       </c>
       <c r="B36" t="n">
-        <v>8441</v>
+        <v>90952</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4979,25 +4979,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589587</v>
+        <v>589637</v>
       </c>
       <c r="R36" t="n">
-        <v>6573386</v>
+        <v>6573466</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -3016,7 +3016,7 @@
         <v>122708106</v>
       </c>
       <c r="B20" t="n">
-        <v>79384</v>
+        <v>79387</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>122781184</v>
       </c>
       <c r="B21" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122790172</v>
+        <v>122781187</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>91365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3257,61 +3257,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589821</v>
+        <v>589525</v>
       </c>
       <c r="R22" t="n">
-        <v>6573637</v>
+        <v>6573444</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3333,57 +3316,47 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3508,10 +3481,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122781185</v>
+        <v>122790172</v>
       </c>
       <c r="B24" t="n">
-        <v>90972</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3520,48 +3493,61 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589591</v>
+        <v>589821</v>
       </c>
       <c r="R24" t="n">
-        <v>6573415</v>
+        <v>6573637</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3583,54 +3569,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122781187</v>
+        <v>122781185</v>
       </c>
       <c r="B25" t="n">
-        <v>91362</v>
+        <v>90975</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3639,28 +3635,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3670,13 +3670,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589525</v>
+        <v>589591</v>
       </c>
       <c r="R25" t="n">
-        <v>6573444</v>
+        <v>6573415</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797980</v>
+        <v>122798013</v>
       </c>
       <c r="B27" t="n">
-        <v>5465</v>
+        <v>4776</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3876,21 +3876,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101377</v>
+        <v>102306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589633</v>
+        <v>589608</v>
       </c>
       <c r="R27" t="n">
-        <v>6573458</v>
+        <v>6573540</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3986,10 +3986,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797974</v>
+        <v>122797987</v>
       </c>
       <c r="B28" t="n">
-        <v>92268</v>
+        <v>90955</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4002,26 +4002,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4033,14 +4033,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589562</v>
+        <v>589638</v>
       </c>
       <c r="R28" t="n">
-        <v>6573423</v>
+        <v>6573473</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122798013</v>
+        <v>122797980</v>
       </c>
       <c r="B29" t="n">
-        <v>4776</v>
+        <v>5465</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4126,21 +4126,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102306</v>
+        <v>101377</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4159,14 +4159,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589608</v>
+        <v>589633</v>
       </c>
       <c r="R29" t="n">
-        <v>6573540</v>
+        <v>6573458</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4236,10 +4236,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122797987</v>
+        <v>122797974</v>
       </c>
       <c r="B30" t="n">
-        <v>90952</v>
+        <v>92271</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4252,26 +4252,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4283,14 +4283,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589638</v>
+        <v>589562</v>
       </c>
       <c r="R30" t="n">
-        <v>6573473</v>
+        <v>6573423</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4363,7 +4363,7 @@
         <v>122797978</v>
       </c>
       <c r="B31" t="n">
-        <v>90972</v>
+        <v>90975</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4631,10 +4631,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122911162</v>
+        <v>122910831</v>
       </c>
       <c r="B33" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4647,21 +4647,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4671,13 +4671,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589636</v>
+        <v>589587</v>
       </c>
       <c r="R33" t="n">
-        <v>6573464</v>
+        <v>6573386</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910831</v>
+        <v>122911262</v>
       </c>
       <c r="B35" t="n">
-        <v>8441</v>
+        <v>90955</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4867,25 +4867,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589587</v>
+        <v>589637</v>
       </c>
       <c r="R35" t="n">
-        <v>6573386</v>
+        <v>6573466</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4967,10 +4967,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122911262</v>
+        <v>122911162</v>
       </c>
       <c r="B36" t="n">
-        <v>90952</v>
+        <v>5173</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4979,25 +4979,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589637</v>
+        <v>589636</v>
       </c>
       <c r="R36" t="n">
-        <v>6573466</v>
+        <v>6573464</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -3016,7 +3016,7 @@
         <v>122708106</v>
       </c>
       <c r="B20" t="n">
-        <v>79387</v>
+        <v>79389</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122781184</v>
+        <v>122790172</v>
       </c>
       <c r="B21" t="n">
-        <v>90920</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,44 +3142,61 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589517</v>
+        <v>589821</v>
       </c>
       <c r="R21" t="n">
-        <v>6573441</v>
+        <v>6573637</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3201,54 +3218,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122781187</v>
+        <v>122781183</v>
       </c>
       <c r="B22" t="n">
-        <v>91365</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3261,26 +3288,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3288,10 +3321,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589525</v>
+        <v>589535</v>
       </c>
       <c r="R22" t="n">
-        <v>6573444</v>
+        <v>6573430</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3323,7 +3356,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3333,7 +3366,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3360,10 +3393,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781183</v>
+        <v>122781185</v>
       </c>
       <c r="B23" t="n">
-        <v>5173</v>
+        <v>90977</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3372,25 +3405,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3400,8 +3433,6 @@
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3409,13 +3440,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589535</v>
+        <v>589591</v>
       </c>
       <c r="R23" t="n">
-        <v>6573430</v>
+        <v>6573415</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3444,7 +3475,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3454,7 +3485,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3481,10 +3512,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122790172</v>
+        <v>122781187</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>91367</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3493,61 +3524,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589821</v>
+        <v>589525</v>
       </c>
       <c r="R24" t="n">
-        <v>6573637</v>
+        <v>6573444</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3569,64 +3583,54 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122781185</v>
+        <v>122781184</v>
       </c>
       <c r="B25" t="n">
-        <v>90975</v>
+        <v>90922</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3635,48 +3639,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589591</v>
+        <v>589517</v>
       </c>
       <c r="R25" t="n">
-        <v>6573415</v>
+        <v>6573441</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3742,10 +3742,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122797991</v>
+        <v>122797974</v>
       </c>
       <c r="B26" t="n">
-        <v>5193</v>
+        <v>92273</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3754,43 +3754,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589638</v>
+        <v>589562</v>
       </c>
       <c r="R26" t="n">
-        <v>6573473</v>
+        <v>6573423</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3860,10 +3866,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122798013</v>
+        <v>122797991</v>
       </c>
       <c r="B27" t="n">
-        <v>4776</v>
+        <v>5193</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3876,47 +3882,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589608</v>
+        <v>589638</v>
       </c>
       <c r="R27" t="n">
-        <v>6573540</v>
+        <v>6573473</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3989,7 +3987,7 @@
         <v>122797987</v>
       </c>
       <c r="B28" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4110,10 +4108,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122797980</v>
+        <v>122797978</v>
       </c>
       <c r="B29" t="n">
-        <v>5465</v>
+        <v>90977</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4122,51 +4120,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101377</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 13, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589633</v>
+        <v>589573</v>
       </c>
       <c r="R29" t="n">
-        <v>6573458</v>
+        <v>6573455</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4236,10 +4232,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122797974</v>
+        <v>122797980</v>
       </c>
       <c r="B30" t="n">
-        <v>92271</v>
+        <v>5465</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4248,49 +4244,51 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5966</v>
+        <v>101377</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589562</v>
+        <v>589633</v>
       </c>
       <c r="R30" t="n">
-        <v>6573423</v>
+        <v>6573458</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4360,10 +4358,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122797978</v>
+        <v>122798013</v>
       </c>
       <c r="B31" t="n">
-        <v>90975</v>
+        <v>4776</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4372,49 +4370,51 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kälbrolund 13, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589573</v>
+        <v>589608</v>
       </c>
       <c r="R31" t="n">
-        <v>6573455</v>
+        <v>6573540</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4631,10 +4631,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122910831</v>
+        <v>122911262</v>
       </c>
       <c r="B33" t="n">
-        <v>8441</v>
+        <v>90957</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4643,25 +4643,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589587</v>
+        <v>589637</v>
       </c>
       <c r="R33" t="n">
-        <v>6573386</v>
+        <v>6573466</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4743,10 +4743,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122910913</v>
+        <v>122910831</v>
       </c>
       <c r="B34" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589562</v>
+        <v>589587</v>
       </c>
       <c r="R34" t="n">
-        <v>6573412</v>
+        <v>6573386</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122911262</v>
+        <v>122910913</v>
       </c>
       <c r="B35" t="n">
-        <v>90955</v>
+        <v>8430</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4867,25 +4867,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589637</v>
+        <v>589562</v>
       </c>
       <c r="R35" t="n">
-        <v>6573466</v>
+        <v>6573412</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -3016,7 +3016,7 @@
         <v>122708106</v>
       </c>
       <c r="B20" t="n">
-        <v>79389</v>
+        <v>79390</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>122790172</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122781183</v>
+        <v>122781185</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>90983</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3284,25 +3284,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3312,8 +3312,6 @@
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3321,13 +3319,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589535</v>
+        <v>589591</v>
       </c>
       <c r="R22" t="n">
-        <v>6573430</v>
+        <v>6573415</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3356,7 +3354,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3366,7 +3364,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3393,10 +3391,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781185</v>
+        <v>122781184</v>
       </c>
       <c r="B23" t="n">
-        <v>90977</v>
+        <v>90928</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3405,48 +3403,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589591</v>
+        <v>589517</v>
       </c>
       <c r="R23" t="n">
-        <v>6573415</v>
+        <v>6573441</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3475,7 +3469,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3485,7 +3479,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3515,7 +3509,7 @@
         <v>122781187</v>
       </c>
       <c r="B24" t="n">
-        <v>91367</v>
+        <v>91373</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3627,10 +3621,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122781184</v>
+        <v>122781183</v>
       </c>
       <c r="B25" t="n">
-        <v>90922</v>
+        <v>5173</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3643,40 +3637,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589517</v>
+        <v>589535</v>
       </c>
       <c r="R25" t="n">
-        <v>6573441</v>
+        <v>6573430</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3742,10 +3742,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122797974</v>
+        <v>122797991</v>
       </c>
       <c r="B26" t="n">
-        <v>92273</v>
+        <v>5193</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3754,49 +3754,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>105930</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589562</v>
+        <v>589638</v>
       </c>
       <c r="R26" t="n">
-        <v>6573423</v>
+        <v>6573473</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3866,10 +3860,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797991</v>
+        <v>122797980</v>
       </c>
       <c r="B27" t="n">
-        <v>5193</v>
+        <v>5465</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3882,39 +3876,47 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>101377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589638</v>
+        <v>589633</v>
       </c>
       <c r="R27" t="n">
-        <v>6573473</v>
+        <v>6573458</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3987,7 +3989,7 @@
         <v>122797987</v>
       </c>
       <c r="B28" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4111,7 +4113,7 @@
         <v>122797978</v>
       </c>
       <c r="B29" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4232,10 +4234,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122797980</v>
+        <v>122798013</v>
       </c>
       <c r="B30" t="n">
-        <v>5465</v>
+        <v>4776</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4248,21 +4250,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101377</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4271,7 +4273,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4281,14 +4283,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589633</v>
+        <v>589608</v>
       </c>
       <c r="R30" t="n">
-        <v>6573458</v>
+        <v>6573540</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4358,10 +4360,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122798013</v>
+        <v>122797974</v>
       </c>
       <c r="B31" t="n">
-        <v>4776</v>
+        <v>92279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4370,51 +4372,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589608</v>
+        <v>589562</v>
       </c>
       <c r="R31" t="n">
-        <v>6573540</v>
+        <v>6573423</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4631,10 +4631,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122911262</v>
+        <v>122911162</v>
       </c>
       <c r="B33" t="n">
-        <v>90957</v>
+        <v>5173</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4643,25 +4643,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4671,13 +4671,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589637</v>
+        <v>589636</v>
       </c>
       <c r="R33" t="n">
-        <v>6573466</v>
+        <v>6573464</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4743,10 +4743,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122910831</v>
+        <v>122910913</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589587</v>
+        <v>589562</v>
       </c>
       <c r="R34" t="n">
-        <v>6573386</v>
+        <v>6573412</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910913</v>
+        <v>122910831</v>
       </c>
       <c r="B35" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589562</v>
+        <v>589587</v>
       </c>
       <c r="R35" t="n">
-        <v>6573412</v>
+        <v>6573386</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4967,10 +4967,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122911162</v>
+        <v>122911262</v>
       </c>
       <c r="B36" t="n">
-        <v>5173</v>
+        <v>90963</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4979,25 +4979,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5007,13 +5007,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589636</v>
+        <v>589637</v>
       </c>
       <c r="R36" t="n">
-        <v>6573464</v>
+        <v>6573466</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -3130,10 +3130,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122790172</v>
+        <v>122781187</v>
       </c>
       <c r="B21" t="n">
-        <v>98376</v>
+        <v>91376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3142,61 +3142,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kälbro 1 km o, Srm</t>
+          <t>Elefantberget, Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589821</v>
+        <v>589525</v>
       </c>
       <c r="R21" t="n">
-        <v>6573637</v>
+        <v>6573444</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3218,64 +3201,54 @@
           <t>Stenkvista</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>D-Esk-0415</t>
-        </is>
-      </c>
       <c r="Y21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122781185</v>
+        <v>122781184</v>
       </c>
       <c r="B22" t="n">
-        <v>90983</v>
+        <v>90931</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3284,48 +3257,44 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Elefantberget, Elefantberget, Srm</t>
+          <t>Elefantberget, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589591</v>
+        <v>589517</v>
       </c>
       <c r="R22" t="n">
-        <v>6573415</v>
+        <v>6573441</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3354,7 +3323,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3364,7 +3333,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3391,10 +3360,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122781184</v>
+        <v>122790172</v>
       </c>
       <c r="B23" t="n">
-        <v>90928</v>
+        <v>98379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3403,44 +3372,61 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vilstadium</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Elefantberget, Srm</t>
+          <t>Kälbro 1 km o, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589517</v>
+        <v>589821</v>
       </c>
       <c r="R23" t="n">
-        <v>6573441</v>
+        <v>6573637</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3462,54 +3448,64 @@
           <t>Stenkvista</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D-Esk-0415</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122781187</v>
+        <v>122781185</v>
       </c>
       <c r="B24" t="n">
-        <v>91373</v>
+        <v>90986</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3518,28 +3514,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -3549,13 +3549,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589525</v>
+        <v>589591</v>
       </c>
       <c r="R24" t="n">
-        <v>6573444</v>
+        <v>6573415</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3742,10 +3742,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122797991</v>
+        <v>122797980</v>
       </c>
       <c r="B26" t="n">
-        <v>5193</v>
+        <v>5465</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3758,39 +3758,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>101377</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 14, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589638</v>
+        <v>589633</v>
       </c>
       <c r="R26" t="n">
-        <v>6573473</v>
+        <v>6573458</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3860,10 +3868,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122797980</v>
+        <v>122797991</v>
       </c>
       <c r="B27" t="n">
-        <v>5465</v>
+        <v>5193</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3876,47 +3884,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101377</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kälbrolund 14, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589633</v>
+        <v>589638</v>
       </c>
       <c r="R27" t="n">
-        <v>6573458</v>
+        <v>6573473</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3986,10 +3986,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122797987</v>
+        <v>122798013</v>
       </c>
       <c r="B28" t="n">
-        <v>90963</v>
+        <v>4776</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3998,49 +3998,51 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kälbrolund 15, Srm</t>
+          <t>Kälbrolund 19, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589638</v>
+        <v>589608</v>
       </c>
       <c r="R28" t="n">
-        <v>6573473</v>
+        <v>6573540</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4110,10 +4112,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122797978</v>
+        <v>122797974</v>
       </c>
       <c r="B29" t="n">
-        <v>90983</v>
+        <v>92282</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4126,21 +4128,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4157,14 +4159,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kälbrolund 13, Srm</t>
+          <t>Kälbrolund 12 oso, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589573</v>
+        <v>589562</v>
       </c>
       <c r="R29" t="n">
-        <v>6573455</v>
+        <v>6573423</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4234,10 +4236,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122798013</v>
+        <v>122797978</v>
       </c>
       <c r="B30" t="n">
-        <v>4776</v>
+        <v>90986</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4246,51 +4248,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälbrolund 19, Srm</t>
+          <t>Kälbrolund 13, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589608</v>
+        <v>589573</v>
       </c>
       <c r="R30" t="n">
-        <v>6573540</v>
+        <v>6573455</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4360,10 +4360,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122797974</v>
+        <v>122797987</v>
       </c>
       <c r="B31" t="n">
-        <v>92279</v>
+        <v>90966</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4376,26 +4376,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4407,14 +4407,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kälbrolund 12 oso, Srm</t>
+          <t>Kälbrolund 15, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589562</v>
+        <v>589638</v>
       </c>
       <c r="R31" t="n">
-        <v>6573423</v>
+        <v>6573473</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122910913</v>
+        <v>122910831</v>
       </c>
       <c r="B34" t="n">
-        <v>8430</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4759,21 +4759,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589562</v>
+        <v>589587</v>
       </c>
       <c r="R34" t="n">
-        <v>6573412</v>
+        <v>6573386</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910831</v>
+        <v>122910913</v>
       </c>
       <c r="B35" t="n">
-        <v>8441</v>
+        <v>8430</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589587</v>
+        <v>589562</v>
       </c>
       <c r="R35" t="n">
-        <v>6573386</v>
+        <v>6573412</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4970,7 +4970,7 @@
         <v>122911262</v>
       </c>
       <c r="B36" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 3859-2025 artfynd.xlsx
+++ b/artfynd/A 3859-2025 artfynd.xlsx
@@ -4634,7 +4634,7 @@
         <v>122911162</v>
       </c>
       <c r="B33" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122910831</v>
+        <v>122911262</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>90983</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4755,25 +4755,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589587</v>
+        <v>589637</v>
       </c>
       <c r="R34" t="n">
-        <v>6573386</v>
+        <v>6573466</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4855,10 +4855,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910913</v>
+        <v>122910831</v>
       </c>
       <c r="B35" t="n">
-        <v>8430</v>
+        <v>8445</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4871,21 +4871,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589562</v>
+        <v>589587</v>
       </c>
       <c r="R35" t="n">
-        <v>6573412</v>
+        <v>6573386</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4967,10 +4967,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122911262</v>
+        <v>122910913</v>
       </c>
       <c r="B36" t="n">
-        <v>90966</v>
+        <v>8434</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4979,25 +4979,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589637</v>
+        <v>589562</v>
       </c>
       <c r="R36" t="n">
-        <v>6573466</v>
+        <v>6573412</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
